--- a/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
+++ b/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
@@ -38,6 +38,9 @@
     <t>tmt.o</t>
   </si>
   <si>
+    <t>led_handle.o</t>
+  </si>
+  <si>
     <t>encoderec11.o</t>
   </si>
   <si>
@@ -59,15 +62,12 @@
     <t>flash_handle.o</t>
   </si>
   <si>
-    <t>led_handle.o</t>
+    <t>beep.o</t>
   </si>
   <si>
     <t>ec11_handle.o</t>
   </si>
   <si>
-    <t>beep.o</t>
-  </si>
-  <si>
     <t>at32f415_int.o</t>
   </si>
   <si>
@@ -89,43 +89,55 @@
     <t>mf_w.l</t>
   </si>
   <si>
+    <t>at32f415_crm.o</t>
+  </si>
+  <si>
+    <t>at32f415_tmr.o</t>
+  </si>
+  <si>
+    <t>at32f415_adc.o</t>
+  </si>
+  <si>
+    <t>at32f415_usart.o</t>
+  </si>
+  <si>
+    <t>at32f415_wk_config.o</t>
+  </si>
+  <si>
+    <t>wk_tmr.o</t>
+  </si>
+  <si>
+    <t>at32f415_gpio.o</t>
+  </si>
+  <si>
+    <t>mc_w.l</t>
+  </si>
+  <si>
+    <t>wk_gpio.o</t>
+  </si>
+  <si>
+    <t>at32f415_misc.o</t>
+  </si>
+  <si>
     <t>at32f415_flash.o</t>
   </si>
   <si>
-    <t>at32f415_crm.o</t>
-  </si>
-  <si>
-    <t>at32f415_tmr.o</t>
-  </si>
-  <si>
-    <t>at32f415_gpio.o</t>
-  </si>
-  <si>
-    <t>wk_tmr.o</t>
-  </si>
-  <si>
-    <t>mc_w.l</t>
-  </si>
-  <si>
-    <t>at32f415_wk_config.o</t>
-  </si>
-  <si>
-    <t>at32f415_usart.o</t>
-  </si>
-  <si>
-    <t>at32f415_adc.o</t>
+    <t>at32f415_dma.o</t>
   </si>
   <si>
     <t>dadd.o</t>
   </si>
   <si>
-    <t>wk_gpio.o</t>
-  </si>
-  <si>
-    <t>at32f415_misc.o</t>
-  </si>
-  <si>
-    <t>at32f415_dma.o</t>
+    <t>util_queue.o</t>
+  </si>
+  <si>
+    <t>wk_adc.o</t>
+  </si>
+  <si>
+    <t>at32f415_crc.o</t>
+  </si>
+  <si>
+    <t>perfc_port_default.o</t>
   </si>
   <si>
     <t>dmul.o</t>
@@ -134,33 +146,27 @@
     <t>ddiv.o</t>
   </si>
   <si>
-    <t>at32f415_crc.o</t>
+    <t>wk_usart.o</t>
   </si>
   <si>
     <t>depilogue.o</t>
   </si>
   <si>
-    <t>wk_adc.o</t>
-  </si>
-  <si>
-    <t>util_queue.o</t>
-  </si>
-  <si>
     <t>fadd.o</t>
   </si>
   <si>
-    <t>wk_usart.o</t>
-  </si>
-  <si>
     <t>fdiv.o</t>
   </si>
   <si>
-    <t>perfc_port_default.o</t>
+    <t>at32f415_wdt.o</t>
   </si>
   <si>
     <t>fepilogue.o</t>
   </si>
   <si>
+    <t>wk_dma.o</t>
+  </si>
+  <si>
     <t>fmul.o</t>
   </si>
   <si>
@@ -173,39 +179,33 @@
     <t>__dczerorl2.o</t>
   </si>
   <si>
-    <t>at32f415_wdt.o</t>
-  </si>
-  <si>
-    <t>wk_dma.o</t>
+    <t>beep_handle.o</t>
   </si>
   <si>
     <t>d2f.o</t>
   </si>
   <si>
+    <t>wk_crc.o</t>
+  </si>
+  <si>
     <t>ffixi.o</t>
   </si>
   <si>
     <t>dfixui.o</t>
   </si>
   <si>
+    <t>flash.o</t>
+  </si>
+  <si>
     <t>init.o</t>
   </si>
   <si>
-    <t>wk_crc.o</t>
-  </si>
-  <si>
-    <t>beep_handle.o</t>
-  </si>
-  <si>
     <t>ffixui.o</t>
   </si>
   <si>
     <t>cpp_init.o</t>
   </si>
   <si>
-    <t>flash.o</t>
-  </si>
-  <si>
     <t>f2d.o</t>
   </si>
   <si>
@@ -239,13 +239,13 @@
     <t>fcmpeq.o</t>
   </si>
   <si>
+    <t>systick_wrapper_gnu.o</t>
+  </si>
+  <si>
+    <t>dfltui.o</t>
+  </si>
+  <si>
     <t>wk_wdt.o</t>
-  </si>
-  <si>
-    <t>systick_wrapper_gnu.o</t>
-  </si>
-  <si>
-    <t>dfltui.o</t>
   </si>
   <si>
     <t>fflti.o</t>
@@ -408,34 +408,34 @@
                   <c:v>tmt.o</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>led_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>encoderec11.o</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>adc_filter.o</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>pid_handle.o</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>output_handle.o</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>key_handle.o</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>perf_counter.o</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>flash_handle.o</c:v>
                 </c:pt>
-                <c:pt idx="13">
-                  <c:v>led_handle.o</c:v>
-                </c:pt>
                 <c:pt idx="14">
+                  <c:v>beep.o</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>ec11_handle.o</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>beep.o</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>at32f415_int.o</c:v>
@@ -468,70 +468,70 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="84"/>
                 <c:pt idx="0">
-                  <c:v>35.06452560424805</c:v>
+                  <c:v>34.10900115966797</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>18.69688415527344</c:v>
+                  <c:v>18.18738555908203</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>16.1158332824707</c:v>
+                  <c:v>15.67666912078857</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.467107772827148</c:v>
+                  <c:v>8.236374855041504</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.469625473022461</c:v>
+                  <c:v>4.34782600402832</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.462385892868042</c:v>
+                  <c:v>3.368034362792969</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.675480127334595</c:v>
+                  <c:v>2.969993829727173</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.266288995742798</c:v>
+                  <c:v>2.617881298065186</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.077431440353394</c:v>
+                  <c:v>2.20453143119812</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.841359734535217</c:v>
+                  <c:v>2.020820617675781</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.652502417564392</c:v>
+                  <c:v>1.974892854690552</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.259049415588379</c:v>
+                  <c:v>1.576852440834045</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.6610009670257568</c:v>
+                  <c:v>1.163502812385559</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.3462385833263397</c:v>
+                  <c:v>0.6889160871505737</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.299024224281311</c:v>
+                  <c:v>0.2602571845054627</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.267547994852066</c:v>
+                  <c:v>0.2449479550123215</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.1888574063777924</c:v>
+                  <c:v>0.1684017181396484</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.06295247375965118</c:v>
+                  <c:v>0.06123698875308037</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.06295247375965118</c:v>
+                  <c:v>0.06123698875308037</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.03147623687982559</c:v>
+                  <c:v>0.03061849437654018</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.0157381184399128</c:v>
+                  <c:v>0.01530924718827009</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.0157381184399128</c:v>
+                  <c:v>0.01530924718827009</c:v>
                 </c:pt>
                 <c:pt idx="83">
                   <c:v>0</c:v>
@@ -608,7 +608,7 @@
                   <c:v>ec11_handle.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>eventrecorder.o</c:v>
+                  <c:v>led_handle.o</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>flash_handle.o</c:v>
@@ -617,178 +617,178 @@
                   <c:v>output_handle.o</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>led_handle.o</c:v>
+                  <c:v>key_handle.o</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>mf_w.l</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>at32f415_flash.o</c:v>
+                  <c:v>at32f415_crm.o</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>at32f415_crm.o</c:v>
+                  <c:v>eventrecorder.o</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>key_handle.o</c:v>
+                  <c:v>encoderec11.o</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>encoderec11.o</c:v>
+                  <c:v>at32f415_tmr.o</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>tmt.o</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>perf_counter.o</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>at32_usart.o</c:v>
                 </c:pt>
-                <c:pt idx="12">
-                  <c:v>at32f415_tmr.o</c:v>
-                </c:pt>
                 <c:pt idx="13">
-                  <c:v>perf_counter.o</c:v>
+                  <c:v>at32f415_adc.o</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>system_at32f415.o</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>pc_comm_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>at32f415_usart.o</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>at32f415_int.o</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>at32f415_wk_config.o</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>main.o</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>wk_tmr.o</c:v>
+                </c:pt>
+                <c:pt idx="21">
                   <c:v>at32f415_gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
-                  <c:v>wk_tmr.o</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>main.o</c:v>
-                </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="22">
                   <c:v>mc_w.l</c:v>
                 </c:pt>
-                <c:pt idx="18">
-                  <c:v>at32f415_int.o</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>at32f415_wk_config.o</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>pc_comm_handle.o</c:v>
-                </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="23">
+                  <c:v>wk_gpio.o</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>at32f415_misc.o</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>pid_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>at32f415_flash.o</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>at32f415_dma.o</c:v>
+                </c:pt>
+                <c:pt idx="28">
                   <c:v>startup_at32f415.o</c:v>
                 </c:pt>
-                <c:pt idx="22">
-                  <c:v>system_at32f415.o</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>at32f415_usart.o</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>at32f415_adc.o</c:v>
-                </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="29">
+                  <c:v>ds201_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>adc_filter.o</c:v>
+                </c:pt>
+                <c:pt idx="31">
                   <c:v>dadd.o</c:v>
                 </c:pt>
-                <c:pt idx="26">
-                  <c:v>wk_gpio.o</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>pid_handle.o</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>adc_filter.o</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>at32f415_misc.o</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>at32f415_dma.o</c:v>
-                </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="32">
+                  <c:v>beep.o</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>util_queue.o</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>key.o</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>wk_adc.o</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>at32f415_crc.o</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>perfc_port_default.o</c:v>
+                </c:pt>
+                <c:pt idx="38">
                   <c:v>dmul.o</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="39">
                   <c:v>ddiv.o</c:v>
                 </c:pt>
-                <c:pt idx="33">
-                  <c:v>at32f415_crc.o</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>ds201_handle.o</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>beep.o</c:v>
-                </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="40">
+                  <c:v>wk_usart.o</c:v>
+                </c:pt>
+                <c:pt idx="41">
                   <c:v>depilogue.o</c:v>
                 </c:pt>
-                <c:pt idx="37">
-                  <c:v>wk_adc.o</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>util_queue.o</c:v>
-                </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="42">
                   <c:v>fadd.o</c:v>
                 </c:pt>
-                <c:pt idx="40">
-                  <c:v>key.o</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>wk_usart.o</c:v>
-                </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="43">
                   <c:v>fdiv.o</c:v>
                 </c:pt>
-                <c:pt idx="43">
-                  <c:v>perfc_port_default.o</c:v>
-                </c:pt>
                 <c:pt idx="44">
+                  <c:v>at32f415_wdt.o</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>wk_system.o</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>iap.o</c:v>
+                </c:pt>
+                <c:pt idx="47">
                   <c:v>fepilogue.o</c:v>
                 </c:pt>
-                <c:pt idx="45">
-                  <c:v>iap.o</c:v>
-                </c:pt>
-                <c:pt idx="46">
+                <c:pt idx="48">
+                  <c:v>wk_dma.o</c:v>
+                </c:pt>
+                <c:pt idx="49">
                   <c:v>fmul.o</c:v>
                 </c:pt>
-                <c:pt idx="47">
+                <c:pt idx="50">
                   <c:v>uldiv.o</c:v>
                 </c:pt>
-                <c:pt idx="48">
+                <c:pt idx="51">
                   <c:v>ldiv.o</c:v>
                 </c:pt>
-                <c:pt idx="49">
+                <c:pt idx="52">
                   <c:v>__dczerorl2.o</c:v>
                 </c:pt>
-                <c:pt idx="50">
-                  <c:v>wk_system.o</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>at32f415_wdt.o</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>wk_dma.o</c:v>
-                </c:pt>
                 <c:pt idx="53">
+                  <c:v>beep_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>d2f.o</c:v>
                 </c:pt>
-                <c:pt idx="54">
+                <c:pt idx="55">
+                  <c:v>wk_crc.o</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>ffixi.o</c:v>
                 </c:pt>
-                <c:pt idx="55">
+                <c:pt idx="57">
                   <c:v>dfixui.o</c:v>
                 </c:pt>
-                <c:pt idx="56">
+                <c:pt idx="58">
+                  <c:v>flash.o</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>init.o</c:v>
                 </c:pt>
-                <c:pt idx="57">
-                  <c:v>wk_crc.o</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>beep_handle.o</c:v>
-                </c:pt>
-                <c:pt idx="59">
+                <c:pt idx="60">
                   <c:v>ffixui.o</c:v>
                 </c:pt>
-                <c:pt idx="60">
+                <c:pt idx="61">
                   <c:v>cpp_init.o</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>flash.o</c:v>
                 </c:pt>
                 <c:pt idx="62">
                   <c:v>f2d.o</c:v>
@@ -824,13 +824,13 @@
                   <c:v>fcmpeq.o</c:v>
                 </c:pt>
                 <c:pt idx="73">
+                  <c:v>systick_wrapper_gnu.o</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>dfltui.o</c:v>
+                </c:pt>
+                <c:pt idx="75">
                   <c:v>wk_wdt.o</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>systick_wrapper_gnu.o</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>dfltui.o</c:v>
                 </c:pt>
                 <c:pt idx="76">
                   <c:v>fflti.o</c:v>
@@ -866,253 +866,253 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="84"/>
                 <c:pt idx="0">
-                  <c:v>12.10966682434082</c:v>
+                  <c:v>17.60184288024902</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>12.0530309677124</c:v>
+                  <c:v>9.62949275970459</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.617711067199707</c:v>
+                  <c:v>9.537326812744141</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.800231456756592</c:v>
+                  <c:v>9.496773719787598</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.697258472442627</c:v>
+                  <c:v>3.646082878112793</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.911828994750977</c:v>
+                  <c:v>3.517050743103027</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.156133413314819</c:v>
+                  <c:v>3.192626714706421</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.574333906173706</c:v>
+                  <c:v>3.129953861236572</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.332346439361572</c:v>
+                  <c:v>2.835022926330566</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.19848108291626</c:v>
+                  <c:v>2.444239616394043</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.038872480392456</c:v>
+                  <c:v>2.071889400482178</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.786587715148926</c:v>
+                  <c:v>1.998156666755676</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.709357738494873</c:v>
+                  <c:v>1.994470000267029</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.683614373207092</c:v>
+                  <c:v>1.681105971336365</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.54974901676178</c:v>
+                  <c:v>1.45990788936615</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.503410935401917</c:v>
+                  <c:v>1.454377889633179</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.477667689323425</c:v>
+                  <c:v>1.389861702919006</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.43647825717926</c:v>
+                  <c:v>1.371428608894348</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.369545578956604</c:v>
+                  <c:v>1.367741942405701</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.050328254699707</c:v>
+                  <c:v>1.301382541656494</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.047753930091858</c:v>
+                  <c:v>1.249769568443298</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.040030837059021</c:v>
+                  <c:v>1.10967743396759</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.029733538627625</c:v>
+                  <c:v>1.028571486473084</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.003990173339844</c:v>
+                  <c:v>0.9548386931419373</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.9113141894340515</c:v>
+                  <c:v>0.9290322661399841</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.8598275184631348</c:v>
+                  <c:v>0.8626728057861328</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.8495301604270935</c:v>
+                  <c:v>0.8552995324134827</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.7620028257369995</c:v>
+                  <c:v>0.7963133454322815</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.6693267822265625</c:v>
+                  <c:v>0.7447004318237305</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.6178401112556458</c:v>
+                  <c:v>0.6746543645858765</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.6126914620399475</c:v>
+                  <c:v>0.6193548440933228</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.5869481563568115</c:v>
+                  <c:v>0.6156681776046753</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.571502149105072</c:v>
+                  <c:v>0.5732718706130981</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.571502149105072</c:v>
+                  <c:v>0.5161290168762207</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.5560561418533325</c:v>
+                  <c:v>0.4626727998256683</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.5225898027420044</c:v>
+                  <c:v>0.4387096762657166</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.478826105594635</c:v>
+                  <c:v>0.4387096762657166</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.4685287773609161</c:v>
+                  <c:v>0.4239631295204163</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.4582314193248749</c:v>
+                  <c:v>0.4202764928340912</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.4530827701091766</c:v>
+                  <c:v>0.409216582775116</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.4144677519798279</c:v>
+                  <c:v>0.3649769723415375</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.4015960991382599</c:v>
+                  <c:v>0.342857152223587</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.3192174136638641</c:v>
+                  <c:v>0.3244239687919617</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.3140687346458435</c:v>
+                  <c:v>0.228571429848671</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.2831767201423645</c:v>
+                  <c:v>0.2175115197896957</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.2728793919086456</c:v>
+                  <c:v>0.2138248831033707</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.2574333846569061</c:v>
+                  <c:v>0.2138248831033707</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.2522847354412079</c:v>
+                  <c:v>0.2027649730443955</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.2522847354412079</c:v>
+                  <c:v>0.1990783363580704</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.2213927209377289</c:v>
+                  <c:v>0.1843318045139313</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.2162440419197083</c:v>
+                  <c:v>0.1806451678276062</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.1699060350656509</c:v>
+                  <c:v>0.1806451678276062</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.1647573709487915</c:v>
+                  <c:v>0.1585253477096558</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.1441626995801926</c:v>
+                  <c:v>0.1253456175327301</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.1287166923284531</c:v>
+                  <c:v>0.1032258048653603</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.1287166923284531</c:v>
+                  <c:v>0.09585253149271011</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.1235680282115936</c:v>
+                  <c:v>0.09216590225696564</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.1235680282115936</c:v>
+                  <c:v>0.09216590225696564</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.1132706925272942</c:v>
+                  <c:v>0.09216590225696564</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.1029733568429947</c:v>
+                  <c:v>0.08847926557064056</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.1029733568429947</c:v>
+                  <c:v>0.07373271882534027</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.1029733568429947</c:v>
+                  <c:v>0.07373271882534027</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.09782468527555466</c:v>
+                  <c:v>0.0700460821390152</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.09267602115869522</c:v>
+                  <c:v>0.06635944545269013</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.09267602115869522</c:v>
+                  <c:v>0.06635944545269013</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.08237868547439575</c:v>
+                  <c:v>0.05898617580533028</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.07723001390695572</c:v>
+                  <c:v>0.0552995391190052</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.07723001390695572</c:v>
+                  <c:v>0.0552995391190052</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.07208134979009628</c:v>
+                  <c:v>0.05161290243268013</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.07208134979009628</c:v>
+                  <c:v>0.05161290243268013</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.07208134979009628</c:v>
+                  <c:v>0.05161290243268013</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.07208134979009628</c:v>
+                  <c:v>0.05161290243268013</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.07208134979009628</c:v>
+                  <c:v>0.05161290243268013</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.07208134979009628</c:v>
+                  <c:v>0.05161290243268013</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.07208134979009628</c:v>
+                  <c:v>0.04792626574635506</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.06693267822265625</c:v>
+                  <c:v>0.04792626574635506</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.04633801057934761</c:v>
+                  <c:v>0.03317972272634506</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.03604067489504814</c:v>
+                  <c:v>0.03317972272634506</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.02574333921074867</c:v>
+                  <c:v>0.01843317970633507</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.02059467136859894</c:v>
+                  <c:v>0.01474654395133257</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.02059467136859894</c:v>
+                  <c:v>0.01474654395133257</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.01029733568429947</c:v>
+                  <c:v>0.007373271975666285</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.01029733568429947</c:v>
+                  <c:v>0.007373271975666285</c:v>
                 </c:pt>
                 <c:pt idx="83">
                   <c:v>0</c:v>
@@ -1579,19 +1579,19 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>35.06452560424805</v>
+        <v>34.10900115966797</v>
       </c>
       <c r="C3" s="1">
         <v>2228</v>
       </c>
       <c r="D3" s="1">
-        <v>694</v>
+        <v>1082</v>
       </c>
       <c r="E3" s="1">
-        <v>678</v>
+        <v>1082</v>
       </c>
       <c r="F3" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -1605,16 +1605,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>18.69688415527344</v>
+        <v>18.18738555908203</v>
       </c>
       <c r="C4" s="1">
         <v>1188</v>
       </c>
       <c r="D4" s="1">
-        <v>4682</v>
+        <v>1698</v>
       </c>
       <c r="E4" s="1">
-        <v>4658</v>
+        <v>1674</v>
       </c>
       <c r="F4" s="1">
         <v>24</v>
@@ -1631,7 +1631,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>16.1158332824707</v>
+        <v>15.67666912078857</v>
       </c>
       <c r="C5" s="1">
         <v>1024</v>
@@ -1657,16 +1657,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>8.467107772827148</v>
+        <v>8.236374855041504</v>
       </c>
       <c r="C6" s="1">
         <v>538</v>
       </c>
       <c r="D6" s="1">
-        <v>407</v>
+        <v>789</v>
       </c>
       <c r="E6" s="1">
-        <v>406</v>
+        <v>788</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -1683,16 +1683,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>4.469625473022461</v>
+        <v>4.34782600402832</v>
       </c>
       <c r="C7" s="1">
         <v>284</v>
       </c>
       <c r="D7" s="1">
-        <v>216</v>
+        <v>366</v>
       </c>
       <c r="E7" s="1">
-        <v>216</v>
+        <v>366</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
@@ -1709,16 +1709,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>3.462385892868042</v>
+        <v>3.368034362792969</v>
       </c>
       <c r="C8" s="1">
         <v>220</v>
       </c>
       <c r="D8" s="1">
-        <v>792</v>
+        <v>1124</v>
       </c>
       <c r="E8" s="1">
-        <v>792</v>
+        <v>1124</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
@@ -1735,25 +1735,25 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>2.675480127334595</v>
+        <v>2.969993829727173</v>
       </c>
       <c r="C9" s="1">
+        <v>194</v>
+      </c>
+      <c r="D9" s="1">
+        <v>5224</v>
+      </c>
+      <c r="E9" s="1">
+        <v>5054</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
         <v>170</v>
       </c>
-      <c r="D9" s="1">
-        <v>854</v>
-      </c>
-      <c r="E9" s="1">
-        <v>686</v>
-      </c>
-      <c r="F9" s="1">
-        <v>0</v>
-      </c>
-      <c r="G9" s="1">
-        <v>168</v>
-      </c>
       <c r="H9" s="1">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1761,25 +1761,25 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>2.266288995742798</v>
+        <v>2.617881298065186</v>
       </c>
       <c r="C10" s="1">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="D10" s="1">
-        <v>260</v>
+        <v>1538</v>
       </c>
       <c r="E10" s="1">
-        <v>260</v>
+        <v>1370</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="H10" s="1">
-        <v>144</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1787,16 +1787,16 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>2.077431440353394</v>
+        <v>2.20453143119812</v>
       </c>
       <c r="C11" s="1">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="D11" s="1">
-        <v>296</v>
+        <v>336</v>
       </c>
       <c r="E11" s="1">
-        <v>296</v>
+        <v>336</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
@@ -1805,7 +1805,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="1">
-        <v>132</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1813,25 +1813,25 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>1.841359734535217</v>
+        <v>2.020820617675781</v>
       </c>
       <c r="C12" s="1">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="D12" s="1">
-        <v>3030</v>
+        <v>468</v>
       </c>
       <c r="E12" s="1">
-        <v>2946</v>
+        <v>468</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>33</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1839,25 +1839,25 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>1.652502417564392</v>
+        <v>1.974892854690552</v>
       </c>
       <c r="C13" s="1">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="D13" s="1">
-        <v>906</v>
+        <v>5152</v>
       </c>
       <c r="E13" s="1">
-        <v>802</v>
+        <v>5060</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="H13" s="1">
-        <v>1</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1865,25 +1865,25 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>1.259049415588379</v>
+        <v>1.576852440834045</v>
       </c>
       <c r="C14" s="1">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="D14" s="1">
-        <v>654</v>
+        <v>1978</v>
       </c>
       <c r="E14" s="1">
-        <v>642</v>
+        <v>1876</v>
       </c>
       <c r="F14" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>8</v>
+        <v>102</v>
       </c>
       <c r="H14" s="1">
-        <v>72</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1891,25 +1891,25 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.6610009670257568</v>
+        <v>1.163502812385559</v>
       </c>
       <c r="C15" s="1">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="D15" s="1">
-        <v>3736</v>
+        <v>1084</v>
       </c>
       <c r="E15" s="1">
-        <v>3736</v>
+        <v>1072</v>
       </c>
       <c r="F15" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H15" s="1">
-        <v>42</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1917,25 +1917,25 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.3462385833263397</v>
+        <v>0.6889160871505737</v>
       </c>
       <c r="C16" s="1">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="D16" s="1">
-        <v>2990</v>
+        <v>5174</v>
       </c>
       <c r="E16" s="1">
-        <v>2904</v>
+        <v>5174</v>
       </c>
       <c r="F16" s="1">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>20</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1943,25 +1943,25 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.299024224281311</v>
+        <v>0.2602571845054627</v>
       </c>
       <c r="C17" s="1">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D17" s="1">
-        <v>4704</v>
+        <v>311</v>
       </c>
       <c r="E17" s="1">
-        <v>4690</v>
+        <v>290</v>
       </c>
       <c r="F17" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G17" s="1">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H17" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1969,25 +1969,25 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.267547994852066</v>
+        <v>0.2449479550123215</v>
       </c>
       <c r="C18" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D18" s="1">
-        <v>203</v>
+        <v>9549</v>
       </c>
       <c r="E18" s="1">
-        <v>182</v>
+        <v>9538</v>
       </c>
       <c r="F18" s="1">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1">
+        <v>11</v>
+      </c>
+      <c r="H18" s="1">
         <v>5</v>
-      </c>
-      <c r="G18" s="1">
-        <v>16</v>
-      </c>
-      <c r="H18" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1995,16 +1995,16 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.1888574063777924</v>
+        <v>0.1684017181396484</v>
       </c>
       <c r="C19" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D19" s="1">
-        <v>532</v>
+        <v>744</v>
       </c>
       <c r="E19" s="1">
-        <v>528</v>
+        <v>740</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -2013,7 +2013,7 @@
         <v>4</v>
       </c>
       <c r="H19" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -2021,16 +2021,16 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.06295247375965118</v>
+        <v>0.06123698875308037</v>
       </c>
       <c r="C20" s="1">
         <v>4</v>
       </c>
       <c r="D20" s="1">
-        <v>84</v>
+        <v>116</v>
       </c>
       <c r="E20" s="1">
-        <v>84</v>
+        <v>116</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -2047,19 +2047,19 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.06295247375965118</v>
+        <v>0.06123698875308037</v>
       </c>
       <c r="C21" s="1">
         <v>4</v>
       </c>
       <c r="D21" s="1">
-        <v>400</v>
+        <v>792</v>
       </c>
       <c r="E21" s="1">
-        <v>396</v>
+        <v>772</v>
       </c>
       <c r="F21" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G21" s="1">
         <v>4</v>
@@ -2073,16 +2073,16 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.03147623687982559</v>
+        <v>0.03061849437654018</v>
       </c>
       <c r="C22" s="1">
         <v>2</v>
       </c>
       <c r="D22" s="1">
-        <v>574</v>
+        <v>706</v>
       </c>
       <c r="E22" s="1">
-        <v>574</v>
+        <v>706</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -2099,16 +2099,16 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.0157381184399128</v>
+        <v>0.01530924718827009</v>
       </c>
       <c r="C23" s="1">
         <v>1</v>
       </c>
       <c r="D23" s="1">
-        <v>161</v>
+        <v>251</v>
       </c>
       <c r="E23" s="1">
-        <v>160</v>
+        <v>250</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
@@ -2125,16 +2125,16 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.0157381184399128</v>
+        <v>0.01530924718827009</v>
       </c>
       <c r="C24" s="1">
         <v>1</v>
       </c>
       <c r="D24" s="1">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="E24" s="1">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -2229,25 +2229,25 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="2">
-        <v>12.10966682434082</v>
+        <v>17.60184288024902</v>
       </c>
       <c r="C3" s="1">
-        <v>4704</v>
+        <v>9549</v>
       </c>
       <c r="D3" s="1">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E3" s="1">
-        <v>4690</v>
+        <v>9538</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H3" s="1">
         <v>5</v>
@@ -2255,45 +2255,45 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B4" s="2">
-        <v>12.0530309677124</v>
+        <v>9.62949275970459</v>
       </c>
       <c r="C4" s="1">
-        <v>4682</v>
+        <v>5224</v>
       </c>
       <c r="D4" s="1">
-        <v>1188</v>
+        <v>194</v>
       </c>
       <c r="E4" s="1">
-        <v>4658</v>
+        <v>5054</v>
       </c>
       <c r="F4" s="1">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1">
+        <v>170</v>
+      </c>
+      <c r="H4" s="1">
         <v>24</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0</v>
-      </c>
-      <c r="H4" s="1">
-        <v>1188</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="2">
-        <v>9.617711067199707</v>
+        <v>9.537326812744141</v>
       </c>
       <c r="C5" s="1">
-        <v>3736</v>
+        <v>5174</v>
       </c>
       <c r="D5" s="1">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E5" s="1">
-        <v>3736</v>
+        <v>5174</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -2302,59 +2302,59 @@
         <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" s="2">
-        <v>7.800231456756592</v>
+        <v>9.496773719787598</v>
       </c>
       <c r="C6" s="1">
-        <v>3030</v>
+        <v>5152</v>
       </c>
       <c r="D6" s="1">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="E6" s="1">
-        <v>2946</v>
+        <v>5060</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="H6" s="1">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B7" s="2">
-        <v>7.697258472442627</v>
+        <v>3.646082878112793</v>
       </c>
       <c r="C7" s="1">
-        <v>2990</v>
+        <v>1978</v>
       </c>
       <c r="D7" s="1">
-        <v>22</v>
+        <v>103</v>
       </c>
       <c r="E7" s="1">
-        <v>2904</v>
+        <v>1876</v>
       </c>
       <c r="F7" s="1">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="H7" s="1">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -2362,7 +2362,7 @@
         <v>23</v>
       </c>
       <c r="B8" s="2">
-        <v>4.911828994750977</v>
+        <v>3.517050743103027</v>
       </c>
       <c r="C8" s="1">
         <v>1908</v>
@@ -2388,19 +2388,19 @@
         <v>24</v>
       </c>
       <c r="B9" s="2">
-        <v>3.156133413314819</v>
+        <v>3.192626714706421</v>
       </c>
       <c r="C9" s="1">
-        <v>1226</v>
+        <v>1732</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
       </c>
       <c r="E9" s="1">
-        <v>1226</v>
+        <v>1692</v>
       </c>
       <c r="F9" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -2411,80 +2411,80 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="B10" s="2">
-        <v>2.574333906173706</v>
+        <v>3.129953861236572</v>
       </c>
       <c r="C10" s="1">
-        <v>1000</v>
+        <v>1698</v>
       </c>
       <c r="D10" s="1">
-        <v>0</v>
+        <v>1188</v>
       </c>
       <c r="E10" s="1">
-        <v>992</v>
+        <v>1674</v>
       </c>
       <c r="F10" s="1">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
       </c>
       <c r="H10" s="1">
-        <v>0</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B11" s="2">
-        <v>2.332346439361572</v>
+        <v>2.835022926330566</v>
       </c>
       <c r="C11" s="1">
-        <v>906</v>
+        <v>1538</v>
       </c>
       <c r="D11" s="1">
-        <v>105</v>
+        <v>171</v>
       </c>
       <c r="E11" s="1">
-        <v>802</v>
+        <v>1370</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>104</v>
+        <v>168</v>
       </c>
       <c r="H11" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="B12" s="2">
-        <v>2.19848108291626</v>
+        <v>2.444239616394043</v>
       </c>
       <c r="C12" s="1">
-        <v>854</v>
+        <v>1326</v>
       </c>
       <c r="D12" s="1">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="E12" s="1">
-        <v>686</v>
+        <v>1326</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -2492,16 +2492,16 @@
         <v>6</v>
       </c>
       <c r="B13" s="2">
-        <v>2.038872480392456</v>
+        <v>2.071889400482178</v>
       </c>
       <c r="C13" s="1">
-        <v>792</v>
+        <v>1124</v>
       </c>
       <c r="D13" s="1">
         <v>220</v>
       </c>
       <c r="E13" s="1">
-        <v>792</v>
+        <v>1124</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
@@ -2515,45 +2515,45 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>1.786587715148926</v>
+        <v>1.998156666755676</v>
       </c>
       <c r="C14" s="1">
-        <v>694</v>
+        <v>1084</v>
       </c>
       <c r="D14" s="1">
-        <v>2228</v>
+        <v>76</v>
       </c>
       <c r="E14" s="1">
-        <v>678</v>
+        <v>1072</v>
       </c>
       <c r="F14" s="1">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H14" s="1">
-        <v>2228</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="B15" s="2">
-        <v>1.709357738494873</v>
+        <v>1.994470000267029</v>
       </c>
       <c r="C15" s="1">
-        <v>664</v>
+        <v>1082</v>
       </c>
       <c r="D15" s="1">
-        <v>0</v>
+        <v>2228</v>
       </c>
       <c r="E15" s="1">
-        <v>664</v>
+        <v>1082</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
@@ -2562,56 +2562,56 @@
         <v>0</v>
       </c>
       <c r="H15" s="1">
-        <v>0</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="B16" s="2">
-        <v>1.683614373207092</v>
+        <v>1.681105971336365</v>
       </c>
       <c r="C16" s="1">
-        <v>654</v>
+        <v>912</v>
       </c>
       <c r="D16" s="1">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="E16" s="1">
-        <v>642</v>
+        <v>912</v>
       </c>
       <c r="F16" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B17" s="2">
-        <v>1.54974901676178</v>
+        <v>1.45990788936615</v>
       </c>
       <c r="C17" s="1">
-        <v>602</v>
+        <v>792</v>
       </c>
       <c r="D17" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E17" s="1">
-        <v>602</v>
+        <v>772</v>
       </c>
       <c r="F17" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H17" s="1">
         <v>0</v>
@@ -2619,45 +2619,45 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="B18" s="2">
-        <v>1.503410935401917</v>
+        <v>1.454377889633179</v>
       </c>
       <c r="C18" s="1">
-        <v>584</v>
+        <v>789</v>
       </c>
       <c r="D18" s="1">
-        <v>0</v>
+        <v>538</v>
       </c>
       <c r="E18" s="1">
-        <v>584</v>
+        <v>788</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" s="1">
-        <v>0</v>
+        <v>537</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B19" s="2">
-        <v>1.477667689323425</v>
+        <v>1.389861702919006</v>
       </c>
       <c r="C19" s="1">
-        <v>574</v>
+        <v>754</v>
       </c>
       <c r="D19" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E19" s="1">
-        <v>574</v>
+        <v>754</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -2666,76 +2666,76 @@
         <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B20" s="2">
-        <v>1.43647825717926</v>
+        <v>1.371428608894348</v>
       </c>
       <c r="C20" s="1">
-        <v>558</v>
+        <v>744</v>
       </c>
       <c r="D20" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E20" s="1">
-        <v>558</v>
+        <v>740</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H20" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B21" s="2">
-        <v>1.369545578956604</v>
+        <v>1.367741942405701</v>
       </c>
       <c r="C21" s="1">
-        <v>532</v>
+        <v>742</v>
       </c>
       <c r="D21" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E21" s="1">
-        <v>528</v>
+        <v>742</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H21" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>1.050328254699707</v>
+        <v>1.301382541656494</v>
       </c>
       <c r="C22" s="1">
-        <v>408</v>
+        <v>706</v>
       </c>
       <c r="D22" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E22" s="1">
-        <v>408</v>
+        <v>706</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -2744,82 +2744,82 @@
         <v>0</v>
       </c>
       <c r="H22" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="B23" s="2">
-        <v>1.047753930091858</v>
+        <v>1.249769568443298</v>
       </c>
       <c r="C23" s="1">
-        <v>407</v>
+        <v>678</v>
       </c>
       <c r="D23" s="1">
-        <v>538</v>
+        <v>0</v>
       </c>
       <c r="E23" s="1">
-        <v>406</v>
+        <v>678</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" s="1">
-        <v>537</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="B24" s="2">
-        <v>1.040030837059021</v>
+        <v>1.10967743396759</v>
       </c>
       <c r="C24" s="1">
-        <v>404</v>
+        <v>602</v>
       </c>
       <c r="D24" s="1">
-        <v>1024</v>
+        <v>0</v>
       </c>
       <c r="E24" s="1">
-        <v>36</v>
+        <v>602</v>
       </c>
       <c r="F24" s="1">
-        <v>368</v>
+        <v>0</v>
       </c>
       <c r="G24" s="1">
         <v>0</v>
       </c>
       <c r="H24" s="1">
-        <v>1024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B25" s="2">
-        <v>1.029733538627625</v>
+        <v>1.028571486473084</v>
       </c>
       <c r="C25" s="1">
-        <v>400</v>
+        <v>558</v>
       </c>
       <c r="D25" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E25" s="1">
-        <v>396</v>
+        <v>558</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H25" s="1">
         <v>0</v>
@@ -2827,19 +2827,19 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B26" s="2">
-        <v>1.003990173339844</v>
+        <v>0.9548386931419373</v>
       </c>
       <c r="C26" s="1">
-        <v>390</v>
+        <v>518</v>
       </c>
       <c r="D26" s="1">
         <v>0</v>
       </c>
       <c r="E26" s="1">
-        <v>390</v>
+        <v>518</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -2853,19 +2853,19 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B27" s="2">
-        <v>0.9113141894340515</v>
+        <v>0.9290322661399841</v>
       </c>
       <c r="C27" s="1">
-        <v>354</v>
+        <v>504</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
       </c>
       <c r="E27" s="1">
-        <v>354</v>
+        <v>504</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
@@ -2879,19 +2879,19 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="B28" s="2">
-        <v>0.8598275184631348</v>
+        <v>0.8626728057861328</v>
       </c>
       <c r="C28" s="1">
-        <v>334</v>
+        <v>468</v>
       </c>
       <c r="D28" s="1">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="E28" s="1">
-        <v>334</v>
+        <v>468</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -2900,7 +2900,7 @@
         <v>0</v>
       </c>
       <c r="H28" s="1">
-        <v>0</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -2908,16 +2908,16 @@
         <v>34</v>
       </c>
       <c r="B29" s="2">
-        <v>0.8495301604270935</v>
+        <v>0.8552995324134827</v>
       </c>
       <c r="C29" s="1">
-        <v>330</v>
+        <v>464</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
       </c>
       <c r="E29" s="1">
-        <v>330</v>
+        <v>464</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
@@ -2931,19 +2931,19 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="B30" s="2">
-        <v>0.7620028257369995</v>
+        <v>0.7963133454322815</v>
       </c>
       <c r="C30" s="1">
-        <v>296</v>
+        <v>432</v>
       </c>
       <c r="D30" s="1">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="E30" s="1">
-        <v>296</v>
+        <v>432</v>
       </c>
       <c r="F30" s="1">
         <v>0</v>
@@ -2952,50 +2952,50 @@
         <v>0</v>
       </c>
       <c r="H30" s="1">
-        <v>132</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B31" s="2">
-        <v>0.6693267822265625</v>
+        <v>0.7447004318237305</v>
       </c>
       <c r="C31" s="1">
-        <v>260</v>
+        <v>404</v>
       </c>
       <c r="D31" s="1">
-        <v>144</v>
+        <v>1024</v>
       </c>
       <c r="E31" s="1">
-        <v>260</v>
+        <v>36</v>
       </c>
       <c r="F31" s="1">
-        <v>0</v>
+        <v>368</v>
       </c>
       <c r="G31" s="1">
         <v>0</v>
       </c>
       <c r="H31" s="1">
-        <v>144</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="B32" s="2">
-        <v>0.6178401112556458</v>
+        <v>0.6746543645858765</v>
       </c>
       <c r="C32" s="1">
-        <v>240</v>
+        <v>366</v>
       </c>
       <c r="D32" s="1">
-        <v>0</v>
+        <v>284</v>
       </c>
       <c r="E32" s="1">
-        <v>240</v>
+        <v>366</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -3004,24 +3004,24 @@
         <v>0</v>
       </c>
       <c r="H32" s="1">
-        <v>0</v>
+        <v>284</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="B33" s="2">
-        <v>0.6126914620399475</v>
+        <v>0.6193548440933228</v>
       </c>
       <c r="C33" s="1">
-        <v>238</v>
+        <v>336</v>
       </c>
       <c r="D33" s="1">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="E33" s="1">
-        <v>238</v>
+        <v>336</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
@@ -3030,24 +3030,24 @@
         <v>0</v>
       </c>
       <c r="H33" s="1">
-        <v>0</v>
+        <v>144</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B34" s="2">
-        <v>0.5869481563568115</v>
+        <v>0.6156681776046753</v>
       </c>
       <c r="C34" s="1">
-        <v>228</v>
+        <v>334</v>
       </c>
       <c r="D34" s="1">
         <v>0</v>
       </c>
       <c r="E34" s="1">
-        <v>228</v>
+        <v>334</v>
       </c>
       <c r="F34" s="1">
         <v>0</v>
@@ -3061,45 +3061,45 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="B35" s="2">
-        <v>0.571502149105072</v>
+        <v>0.5732718706130981</v>
       </c>
       <c r="C35" s="1">
-        <v>222</v>
+        <v>311</v>
       </c>
       <c r="D35" s="1">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E35" s="1">
-        <v>222</v>
+        <v>290</v>
       </c>
       <c r="F35" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G35" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H35" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B36" s="2">
-        <v>0.571502149105072</v>
+        <v>0.5161290168762207</v>
       </c>
       <c r="C36" s="1">
-        <v>222</v>
+        <v>280</v>
       </c>
       <c r="D36" s="1">
         <v>0</v>
       </c>
       <c r="E36" s="1">
-        <v>222</v>
+        <v>280</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
@@ -3113,71 +3113,71 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B37" s="2">
-        <v>0.5560561418533325</v>
+        <v>0.4626727998256683</v>
       </c>
       <c r="C37" s="1">
-        <v>216</v>
+        <v>251</v>
       </c>
       <c r="D37" s="1">
-        <v>284</v>
+        <v>1</v>
       </c>
       <c r="E37" s="1">
-        <v>216</v>
+        <v>250</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
       </c>
       <c r="G37" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" s="1">
-        <v>284</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="B38" s="2">
-        <v>0.5225898027420044</v>
+        <v>0.4387096762657166</v>
       </c>
       <c r="C38" s="1">
-        <v>203</v>
+        <v>238</v>
       </c>
       <c r="D38" s="1">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E38" s="1">
-        <v>182</v>
+        <v>238</v>
       </c>
       <c r="F38" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G38" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H38" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B39" s="2">
-        <v>0.478826105594635</v>
+        <v>0.4387096762657166</v>
       </c>
       <c r="C39" s="1">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="D39" s="1">
         <v>0</v>
       </c>
       <c r="E39" s="1">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="F39" s="1">
         <v>0</v>
@@ -3191,19 +3191,19 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" s="2">
-        <v>0.4685287773609161</v>
+        <v>0.4239631295204163</v>
       </c>
       <c r="C40" s="1">
-        <v>182</v>
+        <v>230</v>
       </c>
       <c r="D40" s="1">
         <v>0</v>
       </c>
       <c r="E40" s="1">
-        <v>182</v>
+        <v>230</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
@@ -3217,19 +3217,19 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B41" s="2">
-        <v>0.4582314193248749</v>
+        <v>0.4202764928340912</v>
       </c>
       <c r="C41" s="1">
-        <v>178</v>
+        <v>228</v>
       </c>
       <c r="D41" s="1">
         <v>0</v>
       </c>
       <c r="E41" s="1">
-        <v>178</v>
+        <v>228</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
@@ -3243,19 +3243,19 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B42" s="2">
-        <v>0.4530827701091766</v>
+        <v>0.409216582775116</v>
       </c>
       <c r="C42" s="1">
-        <v>176</v>
+        <v>222</v>
       </c>
       <c r="D42" s="1">
         <v>0</v>
       </c>
       <c r="E42" s="1">
-        <v>176</v>
+        <v>222</v>
       </c>
       <c r="F42" s="1">
         <v>0</v>
@@ -3269,25 +3269,25 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="B43" s="2">
-        <v>0.4144677519798279</v>
+        <v>0.3649769723415375</v>
       </c>
       <c r="C43" s="1">
-        <v>161</v>
+        <v>198</v>
       </c>
       <c r="D43" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" s="1">
-        <v>160</v>
+        <v>198</v>
       </c>
       <c r="F43" s="1">
         <v>0</v>
       </c>
       <c r="G43" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" s="1">
         <v>0</v>
@@ -3298,16 +3298,16 @@
         <v>44</v>
       </c>
       <c r="B44" s="2">
-        <v>0.4015960991382599</v>
+        <v>0.342857152223587</v>
       </c>
       <c r="C44" s="1">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="D44" s="1">
         <v>0</v>
       </c>
       <c r="E44" s="1">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="F44" s="1">
         <v>0</v>
@@ -3324,16 +3324,16 @@
         <v>45</v>
       </c>
       <c r="B45" s="2">
-        <v>0.3192174136638641</v>
+        <v>0.3244239687919617</v>
       </c>
       <c r="C45" s="1">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="D45" s="1">
         <v>0</v>
       </c>
       <c r="E45" s="1">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
@@ -3350,16 +3350,16 @@
         <v>46</v>
       </c>
       <c r="B46" s="2">
-        <v>0.3140687346458435</v>
+        <v>0.228571429848671</v>
       </c>
       <c r="C46" s="1">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D46" s="1">
         <v>0</v>
       </c>
       <c r="E46" s="1">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
@@ -3376,16 +3376,16 @@
         <v>47</v>
       </c>
       <c r="B47" s="2">
-        <v>0.2831767201423645</v>
+        <v>0.2175115197896957</v>
       </c>
       <c r="C47" s="1">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="D47" s="1">
         <v>0</v>
       </c>
       <c r="E47" s="1">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="F47" s="1">
         <v>0</v>
@@ -3399,19 +3399,19 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B48" s="2">
-        <v>0.2728793919086456</v>
+        <v>0.2138248831033707</v>
       </c>
       <c r="C48" s="1">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="D48" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E48" s="1">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
@@ -3420,24 +3420,24 @@
         <v>0</v>
       </c>
       <c r="H48" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="B49" s="2">
-        <v>0.2574333846569061</v>
+        <v>0.2138248831033707</v>
       </c>
       <c r="C49" s="1">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="D49" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49" s="1">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
@@ -3446,24 +3446,24 @@
         <v>0</v>
       </c>
       <c r="H49" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B50" s="2">
-        <v>0.2522847354412079</v>
+        <v>0.2027649730443955</v>
       </c>
       <c r="C50" s="1">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="D50" s="1">
         <v>0</v>
       </c>
       <c r="E50" s="1">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="F50" s="1">
         <v>0</v>
@@ -3477,19 +3477,19 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B51" s="2">
-        <v>0.2522847354412079</v>
+        <v>0.1990783363580704</v>
       </c>
       <c r="C51" s="1">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
       </c>
       <c r="E51" s="1">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="F51" s="1">
         <v>0</v>
@@ -3503,19 +3503,19 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B52" s="2">
-        <v>0.2213927209377289</v>
+        <v>0.1843318045139313</v>
       </c>
       <c r="C52" s="1">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
       </c>
       <c r="E52" s="1">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
@@ -3529,19 +3529,19 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="B53" s="2">
-        <v>0.2162440419197083</v>
+        <v>0.1806451678276062</v>
       </c>
       <c r="C53" s="1">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="D53" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E53" s="1">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
@@ -3550,7 +3550,7 @@
         <v>0</v>
       </c>
       <c r="H53" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -3558,16 +3558,16 @@
         <v>52</v>
       </c>
       <c r="B54" s="2">
-        <v>0.1699060350656509</v>
+        <v>0.1806451678276062</v>
       </c>
       <c r="C54" s="1">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="D54" s="1">
         <v>0</v>
       </c>
       <c r="E54" s="1">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="F54" s="1">
         <v>0</v>
@@ -3584,16 +3584,16 @@
         <v>53</v>
       </c>
       <c r="B55" s="2">
-        <v>0.1647573709487915</v>
+        <v>0.1585253477096558</v>
       </c>
       <c r="C55" s="1">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="D55" s="1">
         <v>0</v>
       </c>
       <c r="E55" s="1">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="F55" s="1">
         <v>0</v>
@@ -3610,16 +3610,16 @@
         <v>54</v>
       </c>
       <c r="B56" s="2">
-        <v>0.1441626995801926</v>
+        <v>0.1253456175327301</v>
       </c>
       <c r="C56" s="1">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="D56" s="1">
         <v>0</v>
       </c>
       <c r="E56" s="1">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
@@ -3636,16 +3636,16 @@
         <v>55</v>
       </c>
       <c r="B57" s="2">
-        <v>0.1287166923284531</v>
+        <v>0.1032258048653603</v>
       </c>
       <c r="C57" s="1">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D57" s="1">
         <v>0</v>
       </c>
       <c r="E57" s="1">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F57" s="1">
         <v>0</v>
@@ -3662,16 +3662,16 @@
         <v>56</v>
       </c>
       <c r="B58" s="2">
-        <v>0.1287166923284531</v>
+        <v>0.09585253149271011</v>
       </c>
       <c r="C58" s="1">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D58" s="1">
         <v>0</v>
       </c>
       <c r="E58" s="1">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F58" s="1">
         <v>0</v>
@@ -3688,16 +3688,16 @@
         <v>57</v>
       </c>
       <c r="B59" s="2">
-        <v>0.1235680282115936</v>
+        <v>0.09216590225696564</v>
       </c>
       <c r="C59" s="1">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D59" s="1">
         <v>0</v>
       </c>
       <c r="E59" s="1">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F59" s="1">
         <v>0</v>
@@ -3714,16 +3714,16 @@
         <v>58</v>
       </c>
       <c r="B60" s="2">
-        <v>0.1235680282115936</v>
+        <v>0.09216590225696564</v>
       </c>
       <c r="C60" s="1">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D60" s="1">
         <v>0</v>
       </c>
       <c r="E60" s="1">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F60" s="1">
         <v>0</v>
@@ -3740,16 +3740,16 @@
         <v>59</v>
       </c>
       <c r="B61" s="2">
-        <v>0.1132706925272942</v>
+        <v>0.09216590225696564</v>
       </c>
       <c r="C61" s="1">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D61" s="1">
         <v>0</v>
       </c>
       <c r="E61" s="1">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F61" s="1">
         <v>0</v>
@@ -3766,16 +3766,16 @@
         <v>60</v>
       </c>
       <c r="B62" s="2">
-        <v>0.1029733568429947</v>
+        <v>0.08847926557064056</v>
       </c>
       <c r="C62" s="1">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D62" s="1">
         <v>0</v>
       </c>
       <c r="E62" s="1">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F62" s="1">
         <v>0</v>
@@ -3792,7 +3792,7 @@
         <v>61</v>
       </c>
       <c r="B63" s="2">
-        <v>0.1029733568429947</v>
+        <v>0.07373271882534027</v>
       </c>
       <c r="C63" s="1">
         <v>40</v>
@@ -3818,7 +3818,7 @@
         <v>62</v>
       </c>
       <c r="B64" s="2">
-        <v>0.1029733568429947</v>
+        <v>0.07373271882534027</v>
       </c>
       <c r="C64" s="1">
         <v>40</v>
@@ -3844,7 +3844,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="2">
-        <v>0.09782468527555466</v>
+        <v>0.0700460821390152</v>
       </c>
       <c r="C65" s="1">
         <v>38</v>
@@ -3870,7 +3870,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="2">
-        <v>0.09267602115869522</v>
+        <v>0.06635944545269013</v>
       </c>
       <c r="C66" s="1">
         <v>36</v>
@@ -3896,7 +3896,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="2">
-        <v>0.09267602115869522</v>
+        <v>0.06635944545269013</v>
       </c>
       <c r="C67" s="1">
         <v>36</v>
@@ -3922,7 +3922,7 @@
         <v>66</v>
       </c>
       <c r="B68" s="2">
-        <v>0.08237868547439575</v>
+        <v>0.05898617580533028</v>
       </c>
       <c r="C68" s="1">
         <v>32</v>
@@ -3948,7 +3948,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="2">
-        <v>0.07723001390695572</v>
+        <v>0.0552995391190052</v>
       </c>
       <c r="C69" s="1">
         <v>30</v>
@@ -3974,7 +3974,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="2">
-        <v>0.07723001390695572</v>
+        <v>0.0552995391190052</v>
       </c>
       <c r="C70" s="1">
         <v>30</v>
@@ -4000,7 +4000,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="2">
-        <v>0.07208134979009628</v>
+        <v>0.05161290243268013</v>
       </c>
       <c r="C71" s="1">
         <v>28</v>
@@ -4026,7 +4026,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="2">
-        <v>0.07208134979009628</v>
+        <v>0.05161290243268013</v>
       </c>
       <c r="C72" s="1">
         <v>28</v>
@@ -4052,7 +4052,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="2">
-        <v>0.07208134979009628</v>
+        <v>0.05161290243268013</v>
       </c>
       <c r="C73" s="1">
         <v>28</v>
@@ -4078,7 +4078,7 @@
         <v>72</v>
       </c>
       <c r="B74" s="2">
-        <v>0.07208134979009628</v>
+        <v>0.05161290243268013</v>
       </c>
       <c r="C74" s="1">
         <v>28</v>
@@ -4104,7 +4104,7 @@
         <v>73</v>
       </c>
       <c r="B75" s="2">
-        <v>0.07208134979009628</v>
+        <v>0.05161290243268013</v>
       </c>
       <c r="C75" s="1">
         <v>28</v>
@@ -4130,7 +4130,7 @@
         <v>74</v>
       </c>
       <c r="B76" s="2">
-        <v>0.07208134979009628</v>
+        <v>0.05161290243268013</v>
       </c>
       <c r="C76" s="1">
         <v>28</v>
@@ -4156,16 +4156,16 @@
         <v>75</v>
       </c>
       <c r="B77" s="2">
-        <v>0.07208134979009628</v>
+        <v>0.04792626574635506</v>
       </c>
       <c r="C77" s="1">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D77" s="1">
         <v>0</v>
       </c>
       <c r="E77" s="1">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F77" s="1">
         <v>0</v>
@@ -4182,7 +4182,7 @@
         <v>76</v>
       </c>
       <c r="B78" s="2">
-        <v>0.06693267822265625</v>
+        <v>0.04792626574635506</v>
       </c>
       <c r="C78" s="1">
         <v>26</v>
@@ -4208,7 +4208,7 @@
         <v>77</v>
       </c>
       <c r="B79" s="2">
-        <v>0.04633801057934761</v>
+        <v>0.03317972272634506</v>
       </c>
       <c r="C79" s="1">
         <v>18</v>
@@ -4234,16 +4234,16 @@
         <v>78</v>
       </c>
       <c r="B80" s="2">
-        <v>0.03604067489504814</v>
+        <v>0.03317972272634506</v>
       </c>
       <c r="C80" s="1">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D80" s="1">
         <v>0</v>
       </c>
       <c r="E80" s="1">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F80" s="1">
         <v>0</v>
@@ -4260,7 +4260,7 @@
         <v>79</v>
       </c>
       <c r="B81" s="2">
-        <v>0.02574333921074867</v>
+        <v>0.01843317970633507</v>
       </c>
       <c r="C81" s="1">
         <v>10</v>
@@ -4286,7 +4286,7 @@
         <v>80</v>
       </c>
       <c r="B82" s="2">
-        <v>0.02059467136859894</v>
+        <v>0.01474654395133257</v>
       </c>
       <c r="C82" s="1">
         <v>8</v>
@@ -4312,7 +4312,7 @@
         <v>81</v>
       </c>
       <c r="B83" s="2">
-        <v>0.02059467136859894</v>
+        <v>0.01474654395133257</v>
       </c>
       <c r="C83" s="1">
         <v>8</v>
@@ -4338,7 +4338,7 @@
         <v>82</v>
       </c>
       <c r="B84" s="2">
-        <v>0.01029733568429947</v>
+        <v>0.007373271975666285</v>
       </c>
       <c r="C84" s="1">
         <v>4</v>
@@ -4364,7 +4364,7 @@
         <v>83</v>
       </c>
       <c r="B85" s="2">
-        <v>0.01029733568429947</v>
+        <v>0.007373271975666285</v>
       </c>
       <c r="C85" s="1">
         <v>4</v>

--- a/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
+++ b/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
@@ -47,10 +47,10 @@
     <t>adc_filter.o</t>
   </si>
   <si>
+    <t>output_handle.o</t>
+  </si>
+  <si>
     <t>pid_handle.o</t>
-  </si>
-  <si>
-    <t>output_handle.o</t>
   </si>
   <si>
     <t>key_handle.o</t>
@@ -417,10 +417,10 @@
                   <c:v>adc_filter.o</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>output_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>pid_handle.o</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>output_handle.o</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>key_handle.o</c:v>
@@ -468,70 +468,70 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="84"/>
                 <c:pt idx="0">
-                  <c:v>34.10900115966797</c:v>
+                  <c:v>34.01007461547852</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>18.18738555908203</c:v>
+                  <c:v>18.13463592529297</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>15.67666912078857</c:v>
+                  <c:v>15.63120174407959</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.236374855041504</c:v>
+                  <c:v>8.212486267089844</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.34782600402832</c:v>
+                  <c:v>4.396275520324707</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.368034362792969</c:v>
+                  <c:v>3.35826587677002</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.969993829727173</c:v>
+                  <c:v>2.961380004882813</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.617881298065186</c:v>
+                  <c:v>2.610288619995117</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.20453143119812</c:v>
+                  <c:v>2.198137760162354</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.020820617675781</c:v>
+                  <c:v>2.137078285217285</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.974892854690552</c:v>
+                  <c:v>2.014959573745728</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.576852440834045</c:v>
+                  <c:v>1.572279095649719</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.163502812385559</c:v>
+                  <c:v>1.160128235816956</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.6889160871505737</c:v>
+                  <c:v>0.6869180202484131</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.2602571845054627</c:v>
+                  <c:v>0.2595023512840271</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.2449479550123215</c:v>
+                  <c:v>0.2442375272512436</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.1684017181396484</c:v>
+                  <c:v>0.2289726734161377</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.06123698875308037</c:v>
+                  <c:v>0.0610593818128109</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.06123698875308037</c:v>
+                  <c:v>0.0610593818128109</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.03061849437654018</c:v>
+                  <c:v>0.03052969090640545</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.01530924718827009</c:v>
+                  <c:v>0.01526484545320272</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.01530924718827009</c:v>
+                  <c:v>0.01526484545320272</c:v>
                 </c:pt>
                 <c:pt idx="83">
                   <c:v>0</c:v>
@@ -608,13 +608,13 @@
                   <c:v>ec11_handle.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>led_handle.o</c:v>
+                  <c:v>output_handle.o</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>flash_handle.o</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>output_handle.o</c:v>
+                  <c:v>led_handle.o</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>key_handle.o</c:v>
@@ -647,16 +647,16 @@
                   <c:v>at32f415_adc.o</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>at32f415_int.o</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>system_at32f415.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>pc_comm_handle.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>at32f415_usart.o</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>at32f415_int.o</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>at32f415_wk_config.o</c:v>
@@ -866,253 +866,253 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="84"/>
                 <c:pt idx="0">
-                  <c:v>17.60184288024902</c:v>
+                  <c:v>16.9409122467041</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.62949275970459</c:v>
+                  <c:v>12.71503353118897</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.537326812744141</c:v>
+                  <c:v>9.213947296142578</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9.496773719787598</c:v>
+                  <c:v>9.171207427978516</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.646082878112793</c:v>
+                  <c:v>3.41560697555542</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.517050743103027</c:v>
+                  <c:v>3.397799015045166</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.192626714706421</c:v>
+                  <c:v>3.084375143051148</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.129953861236572</c:v>
+                  <c:v>3.023827314376831</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.835022926330566</c:v>
+                  <c:v>2.738896608352661</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.444239616394043</c:v>
+                  <c:v>2.361363410949707</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.071889400482178</c:v>
+                  <c:v>2.001638412475586</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.998156666755676</c:v>
+                  <c:v>1.930405616760254</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.994470000267029</c:v>
+                  <c:v>1.926844000816345</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.681105971336365</c:v>
+                  <c:v>1.624105095863342</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.45990788936615</c:v>
+                  <c:v>1.460269927978516</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.454377889633179</c:v>
+                  <c:v>1.410407066345215</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.389861702919006</c:v>
+                  <c:v>1.405064702033997</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.371428608894348</c:v>
+                  <c:v>1.342736005783081</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.367741942405701</c:v>
+                  <c:v>1.321366190910339</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.301382541656494</c:v>
+                  <c:v>1.257256865501404</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.249769568443298</c:v>
+                  <c:v>1.207394003868103</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.10967743396759</c:v>
+                  <c:v>1.072051882743835</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.028571486473084</c:v>
+                  <c:v>0.9936959147453308</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.9548386931419373</c:v>
+                  <c:v>0.9224632382392883</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.9290322661399841</c:v>
+                  <c:v>0.8975318074226379</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.8626728057861328</c:v>
+                  <c:v>0.8334223628044128</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.8552995324134827</c:v>
+                  <c:v>0.8262991309165955</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.7963133454322815</c:v>
+                  <c:v>0.7693129777908325</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.7447004318237305</c:v>
+                  <c:v>0.719450056552887</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.6746543645858765</c:v>
+                  <c:v>0.6695871949195862</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.6193548440933228</c:v>
+                  <c:v>0.5983545184135437</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.6156681776046753</c:v>
+                  <c:v>0.594792902469635</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.5732718706130981</c:v>
+                  <c:v>0.553834080696106</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.5161290168762207</c:v>
+                  <c:v>0.4986287653446198</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.4626727998256683</c:v>
+                  <c:v>0.4469850659370422</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.4387096762657166</c:v>
+                  <c:v>0.4238344430923462</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.4387096762657166</c:v>
+                  <c:v>0.4238344430923462</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.4239631295204163</c:v>
+                  <c:v>0.4095879197120667</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.4202764928340912</c:v>
+                  <c:v>0.4060262739658356</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.409216582775116</c:v>
+                  <c:v>0.3953413963317871</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.3649769723415375</c:v>
+                  <c:v>0.3526017665863037</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.342857152223587</c:v>
+                  <c:v>0.3312319815158844</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.3244239687919617</c:v>
+                  <c:v>0.3134238123893738</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.228571429848671</c:v>
+                  <c:v>0.2208213061094284</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.2175115197896957</c:v>
+                  <c:v>0.2101364135742188</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.2138248831033707</c:v>
+                  <c:v>0.2065747827291489</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.2138248831033707</c:v>
+                  <c:v>0.2065747827291489</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.2027649730443955</c:v>
+                  <c:v>0.195889875292778</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.1990783363580704</c:v>
+                  <c:v>0.1923282444477081</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.1843318045139313</c:v>
+                  <c:v>0.1780817061662674</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.1806451678276062</c:v>
+                  <c:v>0.1745200753211975</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.1806451678276062</c:v>
+                  <c:v>0.1745200753211975</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.1585253477096558</c:v>
+                  <c:v>0.1531502604484558</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.1253456175327301</c:v>
+                  <c:v>0.1210955604910851</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.1032258048653603</c:v>
+                  <c:v>0.09972575306892395</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.09585253149271011</c:v>
+                  <c:v>0.09260248392820358</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.09216590225696564</c:v>
+                  <c:v>0.0890408530831337</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.09216590225696564</c:v>
+                  <c:v>0.0890408530831337</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.09216590225696564</c:v>
+                  <c:v>0.0890408530831337</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.08847926557064056</c:v>
+                  <c:v>0.08547921478748322</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.07373271882534027</c:v>
+                  <c:v>0.07123268395662308</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.07373271882534027</c:v>
+                  <c:v>0.07123268395662308</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.0700460821390152</c:v>
+                  <c:v>0.0676710456609726</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.06635944545269013</c:v>
+                  <c:v>0.06410941481590271</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.06635944545269013</c:v>
+                  <c:v>0.06410941481590271</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.05898617580533028</c:v>
+                  <c:v>0.05698614567518234</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.0552995391190052</c:v>
+                  <c:v>0.05342451110482216</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.0552995391190052</c:v>
+                  <c:v>0.05342451110482216</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.05161290243268013</c:v>
+                  <c:v>0.04986287653446198</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.05161290243268013</c:v>
+                  <c:v>0.04986287653446198</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.05161290243268013</c:v>
+                  <c:v>0.04986287653446198</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.05161290243268013</c:v>
+                  <c:v>0.04986287653446198</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.05161290243268013</c:v>
+                  <c:v>0.04986287653446198</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.05161290243268013</c:v>
+                  <c:v>0.04986287653446198</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.04792626574635506</c:v>
+                  <c:v>0.04630124196410179</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.04792626574635506</c:v>
+                  <c:v>0.04630124196410179</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.03317972272634506</c:v>
+                  <c:v>0.03205470740795136</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.03317972272634506</c:v>
+                  <c:v>0.03205470740795136</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.01843317970633507</c:v>
+                  <c:v>0.01780817098915577</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.01474654395133257</c:v>
+                  <c:v>0.01424653641879559</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.01474654395133257</c:v>
+                  <c:v>0.01424653641879559</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.007373271975666285</c:v>
+                  <c:v>0.007123268209397793</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.007373271975666285</c:v>
+                  <c:v>0.007123268209397793</c:v>
                 </c:pt>
                 <c:pt idx="83">
                   <c:v>0</c:v>
@@ -1579,7 +1579,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>34.10900115966797</v>
+        <v>34.01007461547852</v>
       </c>
       <c r="C3" s="1">
         <v>2228</v>
@@ -1605,7 +1605,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>18.18738555908203</v>
+        <v>18.13463592529297</v>
       </c>
       <c r="C4" s="1">
         <v>1188</v>
@@ -1631,7 +1631,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>15.67666912078857</v>
+        <v>15.63120174407959</v>
       </c>
       <c r="C5" s="1">
         <v>1024</v>
@@ -1657,7 +1657,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>8.236374855041504</v>
+        <v>8.212486267089844</v>
       </c>
       <c r="C6" s="1">
         <v>538</v>
@@ -1683,16 +1683,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>4.34782600402832</v>
+        <v>4.396275520324707</v>
       </c>
       <c r="C7" s="1">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D7" s="1">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="E7" s="1">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
@@ -1701,7 +1701,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1709,7 +1709,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>3.368034362792969</v>
+        <v>3.35826587677002</v>
       </c>
       <c r="C8" s="1">
         <v>220</v>
@@ -1735,16 +1735,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>2.969993829727173</v>
+        <v>2.961380004882813</v>
       </c>
       <c r="C9" s="1">
         <v>194</v>
       </c>
       <c r="D9" s="1">
-        <v>5224</v>
+        <v>5150</v>
       </c>
       <c r="E9" s="1">
-        <v>5054</v>
+        <v>4980</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -1761,7 +1761,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>2.617881298065186</v>
+        <v>2.610288619995117</v>
       </c>
       <c r="C10" s="1">
         <v>171</v>
@@ -1787,7 +1787,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>2.20453143119812</v>
+        <v>2.198137760162354</v>
       </c>
       <c r="C11" s="1">
         <v>144</v>
@@ -1813,25 +1813,25 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>2.020820617675781</v>
+        <v>2.137078285217285</v>
       </c>
       <c r="C12" s="1">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="D12" s="1">
-        <v>468</v>
+        <v>7140</v>
       </c>
       <c r="E12" s="1">
-        <v>468</v>
+        <v>7040</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>132</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1839,25 +1839,25 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>1.974892854690552</v>
+        <v>2.014959573745728</v>
       </c>
       <c r="C13" s="1">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D13" s="1">
-        <v>5152</v>
+        <v>468</v>
       </c>
       <c r="E13" s="1">
-        <v>5060</v>
+        <v>468</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="H13" s="1">
-        <v>37</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1865,16 +1865,16 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>1.576852440834045</v>
+        <v>1.572279095649719</v>
       </c>
       <c r="C14" s="1">
         <v>103</v>
       </c>
       <c r="D14" s="1">
-        <v>1978</v>
+        <v>1918</v>
       </c>
       <c r="E14" s="1">
-        <v>1876</v>
+        <v>1816</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -1891,7 +1891,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>1.163502812385559</v>
+        <v>1.160128235816956</v>
       </c>
       <c r="C15" s="1">
         <v>76</v>
@@ -1917,7 +1917,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.6889160871505737</v>
+        <v>0.6869180202484131</v>
       </c>
       <c r="C16" s="1">
         <v>45</v>
@@ -1943,7 +1943,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.2602571845054627</v>
+        <v>0.2595023512840271</v>
       </c>
       <c r="C17" s="1">
         <v>17</v>
@@ -1969,16 +1969,16 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.2449479550123215</v>
+        <v>0.2442375272512436</v>
       </c>
       <c r="C18" s="1">
         <v>16</v>
       </c>
       <c r="D18" s="1">
-        <v>9549</v>
+        <v>9513</v>
       </c>
       <c r="E18" s="1">
-        <v>9538</v>
+        <v>9502</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -1995,22 +1995,22 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.1684017181396484</v>
+        <v>0.2289726734161377</v>
       </c>
       <c r="C19" s="1">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D19" s="1">
-        <v>744</v>
+        <v>820</v>
       </c>
       <c r="E19" s="1">
-        <v>740</v>
+        <v>812</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H19" s="1">
         <v>7</v>
@@ -2021,7 +2021,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.06123698875308037</v>
+        <v>0.0610593818128109</v>
       </c>
       <c r="C20" s="1">
         <v>4</v>
@@ -2047,7 +2047,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.06123698875308037</v>
+        <v>0.0610593818128109</v>
       </c>
       <c r="C21" s="1">
         <v>4</v>
@@ -2073,7 +2073,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.03061849437654018</v>
+        <v>0.03052969090640545</v>
       </c>
       <c r="C22" s="1">
         <v>2</v>
@@ -2099,7 +2099,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.01530924718827009</v>
+        <v>0.01526484545320272</v>
       </c>
       <c r="C23" s="1">
         <v>1</v>
@@ -2125,7 +2125,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.01530924718827009</v>
+        <v>0.01526484545320272</v>
       </c>
       <c r="C24" s="1">
         <v>1</v>
@@ -2232,16 +2232,16 @@
         <v>16</v>
       </c>
       <c r="B3" s="2">
-        <v>17.60184288024902</v>
+        <v>16.9409122467041</v>
       </c>
       <c r="C3" s="1">
-        <v>9549</v>
+        <v>9513</v>
       </c>
       <c r="D3" s="1">
         <v>16</v>
       </c>
       <c r="E3" s="1">
-        <v>9538</v>
+        <v>9502</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -2255,28 +2255,28 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" s="2">
-        <v>9.62949275970459</v>
+        <v>12.71503353118897</v>
       </c>
       <c r="C4" s="1">
-        <v>5224</v>
+        <v>7140</v>
       </c>
       <c r="D4" s="1">
-        <v>194</v>
+        <v>140</v>
       </c>
       <c r="E4" s="1">
-        <v>5054</v>
+        <v>7040</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2284,7 +2284,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="2">
-        <v>9.537326812744141</v>
+        <v>9.213947296142578</v>
       </c>
       <c r="C5" s="1">
         <v>5174</v>
@@ -2307,28 +2307,28 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B6" s="2">
-        <v>9.496773719787598</v>
+        <v>9.171207427978516</v>
       </c>
       <c r="C6" s="1">
-        <v>5152</v>
+        <v>5150</v>
       </c>
       <c r="D6" s="1">
-        <v>129</v>
+        <v>194</v>
       </c>
       <c r="E6" s="1">
-        <v>5060</v>
+        <v>4980</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>92</v>
+        <v>170</v>
       </c>
       <c r="H6" s="1">
-        <v>37</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -2336,16 +2336,16 @@
         <v>12</v>
       </c>
       <c r="B7" s="2">
-        <v>3.646082878112793</v>
+        <v>3.41560697555542</v>
       </c>
       <c r="C7" s="1">
-        <v>1978</v>
+        <v>1918</v>
       </c>
       <c r="D7" s="1">
         <v>103</v>
       </c>
       <c r="E7" s="1">
-        <v>1876</v>
+        <v>1816</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
@@ -2362,7 +2362,7 @@
         <v>23</v>
       </c>
       <c r="B8" s="2">
-        <v>3.517050743103027</v>
+        <v>3.397799015045166</v>
       </c>
       <c r="C8" s="1">
         <v>1908</v>
@@ -2388,7 +2388,7 @@
         <v>24</v>
       </c>
       <c r="B9" s="2">
-        <v>3.192626714706421</v>
+        <v>3.084375143051148</v>
       </c>
       <c r="C9" s="1">
         <v>1732</v>
@@ -2414,7 +2414,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="2">
-        <v>3.129953861236572</v>
+        <v>3.023827314376831</v>
       </c>
       <c r="C10" s="1">
         <v>1698</v>
@@ -2440,7 +2440,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="2">
-        <v>2.835022926330566</v>
+        <v>2.738896608352661</v>
       </c>
       <c r="C11" s="1">
         <v>1538</v>
@@ -2466,7 +2466,7 @@
         <v>25</v>
       </c>
       <c r="B12" s="2">
-        <v>2.444239616394043</v>
+        <v>2.361363410949707</v>
       </c>
       <c r="C12" s="1">
         <v>1326</v>
@@ -2492,7 +2492,7 @@
         <v>6</v>
       </c>
       <c r="B13" s="2">
-        <v>2.071889400482178</v>
+        <v>2.001638412475586</v>
       </c>
       <c r="C13" s="1">
         <v>1124</v>
@@ -2518,7 +2518,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>1.998156666755676</v>
+        <v>1.930405616760254</v>
       </c>
       <c r="C14" s="1">
         <v>1084</v>
@@ -2544,7 +2544,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="2">
-        <v>1.994470000267029</v>
+        <v>1.926844000816345</v>
       </c>
       <c r="C15" s="1">
         <v>1082</v>
@@ -2570,7 +2570,7 @@
         <v>26</v>
       </c>
       <c r="B16" s="2">
-        <v>1.681105971336365</v>
+        <v>1.624105095863342</v>
       </c>
       <c r="C16" s="1">
         <v>912</v>
@@ -2593,106 +2593,106 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B17" s="2">
-        <v>1.45990788936615</v>
+        <v>1.460269927978516</v>
       </c>
       <c r="C17" s="1">
-        <v>792</v>
+        <v>820</v>
       </c>
       <c r="D17" s="1">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E17" s="1">
-        <v>772</v>
+        <v>812</v>
       </c>
       <c r="F17" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H17" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="2">
+        <v>1.410407066345215</v>
+      </c>
+      <c r="C18" s="1">
+        <v>792</v>
+      </c>
+      <c r="D18" s="1">
         <v>4</v>
       </c>
-      <c r="B18" s="2">
-        <v>1.454377889633179</v>
-      </c>
-      <c r="C18" s="1">
-        <v>789</v>
-      </c>
-      <c r="D18" s="1">
-        <v>538</v>
-      </c>
       <c r="E18" s="1">
-        <v>788</v>
+        <v>772</v>
       </c>
       <c r="F18" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G18" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H18" s="1">
-        <v>537</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="B19" s="2">
-        <v>1.389861702919006</v>
+        <v>1.405064702033997</v>
       </c>
       <c r="C19" s="1">
-        <v>754</v>
+        <v>789</v>
       </c>
       <c r="D19" s="1">
-        <v>0</v>
+        <v>538</v>
       </c>
       <c r="E19" s="1">
-        <v>754</v>
+        <v>788</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="1">
-        <v>0</v>
+        <v>537</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B20" s="2">
-        <v>1.371428608894348</v>
+        <v>1.342736005783081</v>
       </c>
       <c r="C20" s="1">
-        <v>744</v>
+        <v>754</v>
       </c>
       <c r="D20" s="1">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E20" s="1">
-        <v>740</v>
+        <v>754</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H20" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -2700,7 +2700,7 @@
         <v>28</v>
       </c>
       <c r="B21" s="2">
-        <v>1.367741942405701</v>
+        <v>1.321366190910339</v>
       </c>
       <c r="C21" s="1">
         <v>742</v>
@@ -2726,7 +2726,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>1.301382541656494</v>
+        <v>1.257256865501404</v>
       </c>
       <c r="C22" s="1">
         <v>706</v>
@@ -2752,7 +2752,7 @@
         <v>29</v>
       </c>
       <c r="B23" s="2">
-        <v>1.249769568443298</v>
+        <v>1.207394003868103</v>
       </c>
       <c r="C23" s="1">
         <v>678</v>
@@ -2778,7 +2778,7 @@
         <v>30</v>
       </c>
       <c r="B24" s="2">
-        <v>1.10967743396759</v>
+        <v>1.072051882743835</v>
       </c>
       <c r="C24" s="1">
         <v>602</v>
@@ -2804,7 +2804,7 @@
         <v>31</v>
       </c>
       <c r="B25" s="2">
-        <v>1.028571486473084</v>
+        <v>0.9936959147453308</v>
       </c>
       <c r="C25" s="1">
         <v>558</v>
@@ -2830,7 +2830,7 @@
         <v>32</v>
       </c>
       <c r="B26" s="2">
-        <v>0.9548386931419373</v>
+        <v>0.9224632382392883</v>
       </c>
       <c r="C26" s="1">
         <v>518</v>
@@ -2856,7 +2856,7 @@
         <v>33</v>
       </c>
       <c r="B27" s="2">
-        <v>0.9290322661399841</v>
+        <v>0.8975318074226379</v>
       </c>
       <c r="C27" s="1">
         <v>504</v>
@@ -2879,10 +2879,10 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B28" s="2">
-        <v>0.8626728057861328</v>
+        <v>0.8334223628044128</v>
       </c>
       <c r="C28" s="1">
         <v>468</v>
@@ -2908,7 +2908,7 @@
         <v>34</v>
       </c>
       <c r="B29" s="2">
-        <v>0.8552995324134827</v>
+        <v>0.8262991309165955</v>
       </c>
       <c r="C29" s="1">
         <v>464</v>
@@ -2934,7 +2934,7 @@
         <v>35</v>
       </c>
       <c r="B30" s="2">
-        <v>0.7963133454322815</v>
+        <v>0.7693129777908325</v>
       </c>
       <c r="C30" s="1">
         <v>432</v>
@@ -2960,7 +2960,7 @@
         <v>3</v>
       </c>
       <c r="B31" s="2">
-        <v>0.7447004318237305</v>
+        <v>0.719450056552887</v>
       </c>
       <c r="C31" s="1">
         <v>404</v>
@@ -2986,16 +2986,16 @@
         <v>5</v>
       </c>
       <c r="B32" s="2">
-        <v>0.6746543645858765</v>
+        <v>0.6695871949195862</v>
       </c>
       <c r="C32" s="1">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="D32" s="1">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E32" s="1">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -3004,7 +3004,7 @@
         <v>0</v>
       </c>
       <c r="H32" s="1">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -3012,7 +3012,7 @@
         <v>9</v>
       </c>
       <c r="B33" s="2">
-        <v>0.6193548440933228</v>
+        <v>0.5983545184135437</v>
       </c>
       <c r="C33" s="1">
         <v>336</v>
@@ -3038,7 +3038,7 @@
         <v>36</v>
       </c>
       <c r="B34" s="2">
-        <v>0.6156681776046753</v>
+        <v>0.594792902469635</v>
       </c>
       <c r="C34" s="1">
         <v>334</v>
@@ -3064,7 +3064,7 @@
         <v>15</v>
       </c>
       <c r="B35" s="2">
-        <v>0.5732718706130981</v>
+        <v>0.553834080696106</v>
       </c>
       <c r="C35" s="1">
         <v>311</v>
@@ -3090,7 +3090,7 @@
         <v>37</v>
       </c>
       <c r="B36" s="2">
-        <v>0.5161290168762207</v>
+        <v>0.4986287653446198</v>
       </c>
       <c r="C36" s="1">
         <v>280</v>
@@ -3116,7 +3116,7 @@
         <v>21</v>
       </c>
       <c r="B37" s="2">
-        <v>0.4626727998256683</v>
+        <v>0.4469850659370422</v>
       </c>
       <c r="C37" s="1">
         <v>251</v>
@@ -3142,7 +3142,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="2">
-        <v>0.4387096762657166</v>
+        <v>0.4238344430923462</v>
       </c>
       <c r="C38" s="1">
         <v>238</v>
@@ -3168,7 +3168,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="2">
-        <v>0.4387096762657166</v>
+        <v>0.4238344430923462</v>
       </c>
       <c r="C39" s="1">
         <v>238</v>
@@ -3194,7 +3194,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="2">
-        <v>0.4239631295204163</v>
+        <v>0.4095879197120667</v>
       </c>
       <c r="C40" s="1">
         <v>230</v>
@@ -3220,7 +3220,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="2">
-        <v>0.4202764928340912</v>
+        <v>0.4060262739658356</v>
       </c>
       <c r="C41" s="1">
         <v>228</v>
@@ -3246,7 +3246,7 @@
         <v>42</v>
       </c>
       <c r="B42" s="2">
-        <v>0.409216582775116</v>
+        <v>0.3953413963317871</v>
       </c>
       <c r="C42" s="1">
         <v>222</v>
@@ -3272,7 +3272,7 @@
         <v>43</v>
       </c>
       <c r="B43" s="2">
-        <v>0.3649769723415375</v>
+        <v>0.3526017665863037</v>
       </c>
       <c r="C43" s="1">
         <v>198</v>
@@ -3298,7 +3298,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="2">
-        <v>0.342857152223587</v>
+        <v>0.3312319815158844</v>
       </c>
       <c r="C44" s="1">
         <v>186</v>
@@ -3324,7 +3324,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="2">
-        <v>0.3244239687919617</v>
+        <v>0.3134238123893738</v>
       </c>
       <c r="C45" s="1">
         <v>176</v>
@@ -3350,7 +3350,7 @@
         <v>46</v>
       </c>
       <c r="B46" s="2">
-        <v>0.228571429848671</v>
+        <v>0.2208213061094284</v>
       </c>
       <c r="C46" s="1">
         <v>124</v>
@@ -3376,7 +3376,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="2">
-        <v>0.2175115197896957</v>
+        <v>0.2101364135742188</v>
       </c>
       <c r="C47" s="1">
         <v>118</v>
@@ -3402,7 +3402,7 @@
         <v>18</v>
       </c>
       <c r="B48" s="2">
-        <v>0.2138248831033707</v>
+        <v>0.2065747827291489</v>
       </c>
       <c r="C48" s="1">
         <v>116</v>
@@ -3428,7 +3428,7 @@
         <v>22</v>
       </c>
       <c r="B49" s="2">
-        <v>0.2138248831033707</v>
+        <v>0.2065747827291489</v>
       </c>
       <c r="C49" s="1">
         <v>116</v>
@@ -3454,7 +3454,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="2">
-        <v>0.2027649730443955</v>
+        <v>0.195889875292778</v>
       </c>
       <c r="C50" s="1">
         <v>110</v>
@@ -3480,7 +3480,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="2">
-        <v>0.1990783363580704</v>
+        <v>0.1923282444477081</v>
       </c>
       <c r="C51" s="1">
         <v>108</v>
@@ -3506,7 +3506,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="2">
-        <v>0.1843318045139313</v>
+        <v>0.1780817061662674</v>
       </c>
       <c r="C52" s="1">
         <v>100</v>
@@ -3532,7 +3532,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="2">
-        <v>0.1806451678276062</v>
+        <v>0.1745200753211975</v>
       </c>
       <c r="C53" s="1">
         <v>98</v>
@@ -3558,7 +3558,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="2">
-        <v>0.1806451678276062</v>
+        <v>0.1745200753211975</v>
       </c>
       <c r="C54" s="1">
         <v>98</v>
@@ -3584,7 +3584,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="2">
-        <v>0.1585253477096558</v>
+        <v>0.1531502604484558</v>
       </c>
       <c r="C55" s="1">
         <v>86</v>
@@ -3610,7 +3610,7 @@
         <v>54</v>
       </c>
       <c r="B56" s="2">
-        <v>0.1253456175327301</v>
+        <v>0.1210955604910851</v>
       </c>
       <c r="C56" s="1">
         <v>68</v>
@@ -3636,7 +3636,7 @@
         <v>55</v>
       </c>
       <c r="B57" s="2">
-        <v>0.1032258048653603</v>
+        <v>0.09972575306892395</v>
       </c>
       <c r="C57" s="1">
         <v>56</v>
@@ -3662,7 +3662,7 @@
         <v>56</v>
       </c>
       <c r="B58" s="2">
-        <v>0.09585253149271011</v>
+        <v>0.09260248392820358</v>
       </c>
       <c r="C58" s="1">
         <v>52</v>
@@ -3688,7 +3688,7 @@
         <v>57</v>
       </c>
       <c r="B59" s="2">
-        <v>0.09216590225696564</v>
+        <v>0.0890408530831337</v>
       </c>
       <c r="C59" s="1">
         <v>50</v>
@@ -3714,7 +3714,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="2">
-        <v>0.09216590225696564</v>
+        <v>0.0890408530831337</v>
       </c>
       <c r="C60" s="1">
         <v>50</v>
@@ -3740,7 +3740,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="2">
-        <v>0.09216590225696564</v>
+        <v>0.0890408530831337</v>
       </c>
       <c r="C61" s="1">
         <v>50</v>
@@ -3766,7 +3766,7 @@
         <v>60</v>
       </c>
       <c r="B62" s="2">
-        <v>0.08847926557064056</v>
+        <v>0.08547921478748322</v>
       </c>
       <c r="C62" s="1">
         <v>48</v>
@@ -3792,7 +3792,7 @@
         <v>61</v>
       </c>
       <c r="B63" s="2">
-        <v>0.07373271882534027</v>
+        <v>0.07123268395662308</v>
       </c>
       <c r="C63" s="1">
         <v>40</v>
@@ -3818,7 +3818,7 @@
         <v>62</v>
       </c>
       <c r="B64" s="2">
-        <v>0.07373271882534027</v>
+        <v>0.07123268395662308</v>
       </c>
       <c r="C64" s="1">
         <v>40</v>
@@ -3844,7 +3844,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="2">
-        <v>0.0700460821390152</v>
+        <v>0.0676710456609726</v>
       </c>
       <c r="C65" s="1">
         <v>38</v>
@@ -3870,7 +3870,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="2">
-        <v>0.06635944545269013</v>
+        <v>0.06410941481590271</v>
       </c>
       <c r="C66" s="1">
         <v>36</v>
@@ -3896,7 +3896,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="2">
-        <v>0.06635944545269013</v>
+        <v>0.06410941481590271</v>
       </c>
       <c r="C67" s="1">
         <v>36</v>
@@ -3922,7 +3922,7 @@
         <v>66</v>
       </c>
       <c r="B68" s="2">
-        <v>0.05898617580533028</v>
+        <v>0.05698614567518234</v>
       </c>
       <c r="C68" s="1">
         <v>32</v>
@@ -3948,7 +3948,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="2">
-        <v>0.0552995391190052</v>
+        <v>0.05342451110482216</v>
       </c>
       <c r="C69" s="1">
         <v>30</v>
@@ -3974,7 +3974,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="2">
-        <v>0.0552995391190052</v>
+        <v>0.05342451110482216</v>
       </c>
       <c r="C70" s="1">
         <v>30</v>
@@ -4000,7 +4000,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="2">
-        <v>0.05161290243268013</v>
+        <v>0.04986287653446198</v>
       </c>
       <c r="C71" s="1">
         <v>28</v>
@@ -4026,7 +4026,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="2">
-        <v>0.05161290243268013</v>
+        <v>0.04986287653446198</v>
       </c>
       <c r="C72" s="1">
         <v>28</v>
@@ -4052,7 +4052,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="2">
-        <v>0.05161290243268013</v>
+        <v>0.04986287653446198</v>
       </c>
       <c r="C73" s="1">
         <v>28</v>
@@ -4078,7 +4078,7 @@
         <v>72</v>
       </c>
       <c r="B74" s="2">
-        <v>0.05161290243268013</v>
+        <v>0.04986287653446198</v>
       </c>
       <c r="C74" s="1">
         <v>28</v>
@@ -4104,7 +4104,7 @@
         <v>73</v>
       </c>
       <c r="B75" s="2">
-        <v>0.05161290243268013</v>
+        <v>0.04986287653446198</v>
       </c>
       <c r="C75" s="1">
         <v>28</v>
@@ -4130,7 +4130,7 @@
         <v>74</v>
       </c>
       <c r="B76" s="2">
-        <v>0.05161290243268013</v>
+        <v>0.04986287653446198</v>
       </c>
       <c r="C76" s="1">
         <v>28</v>
@@ -4156,7 +4156,7 @@
         <v>75</v>
       </c>
       <c r="B77" s="2">
-        <v>0.04792626574635506</v>
+        <v>0.04630124196410179</v>
       </c>
       <c r="C77" s="1">
         <v>26</v>
@@ -4182,7 +4182,7 @@
         <v>76</v>
       </c>
       <c r="B78" s="2">
-        <v>0.04792626574635506</v>
+        <v>0.04630124196410179</v>
       </c>
       <c r="C78" s="1">
         <v>26</v>
@@ -4208,7 +4208,7 @@
         <v>77</v>
       </c>
       <c r="B79" s="2">
-        <v>0.03317972272634506</v>
+        <v>0.03205470740795136</v>
       </c>
       <c r="C79" s="1">
         <v>18</v>
@@ -4234,7 +4234,7 @@
         <v>78</v>
       </c>
       <c r="B80" s="2">
-        <v>0.03317972272634506</v>
+        <v>0.03205470740795136</v>
       </c>
       <c r="C80" s="1">
         <v>18</v>
@@ -4260,7 +4260,7 @@
         <v>79</v>
       </c>
       <c r="B81" s="2">
-        <v>0.01843317970633507</v>
+        <v>0.01780817098915577</v>
       </c>
       <c r="C81" s="1">
         <v>10</v>
@@ -4286,7 +4286,7 @@
         <v>80</v>
       </c>
       <c r="B82" s="2">
-        <v>0.01474654395133257</v>
+        <v>0.01424653641879559</v>
       </c>
       <c r="C82" s="1">
         <v>8</v>
@@ -4312,7 +4312,7 @@
         <v>81</v>
       </c>
       <c r="B83" s="2">
-        <v>0.01474654395133257</v>
+        <v>0.01424653641879559</v>
       </c>
       <c r="C83" s="1">
         <v>8</v>
@@ -4338,7 +4338,7 @@
         <v>82</v>
       </c>
       <c r="B84" s="2">
-        <v>0.007373271975666285</v>
+        <v>0.007123268209397793</v>
       </c>
       <c r="C84" s="1">
         <v>4</v>
@@ -4364,7 +4364,7 @@
         <v>83</v>
       </c>
       <c r="B85" s="2">
-        <v>0.007373271975666285</v>
+        <v>0.007123268209397793</v>
       </c>
       <c r="C85" s="1">
         <v>4</v>

--- a/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
+++ b/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
@@ -15,12 +15,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="51">
   <si>
     <t>AT32F415RBT7_WorkBench</t>
   </si>
   <si>
-    <t>lto-llvm-bc9b39.o</t>
+    <t>lto-llvm-44c51f.o</t>
   </si>
   <si>
     <t>startup_at32f415.o</t>
@@ -38,12 +38,18 @@
     <t>dmul.o</t>
   </si>
   <si>
+    <t>ddiv.o</t>
+  </si>
+  <si>
     <t>depilogue.o</t>
   </si>
   <si>
     <t>fadd.o</t>
   </si>
   <si>
+    <t>fdiv.o</t>
+  </si>
+  <si>
     <t>fepilogue.o</t>
   </si>
   <si>
@@ -51,6 +57,9 @@
   </si>
   <si>
     <t>uldiv.o</t>
+  </si>
+  <si>
+    <t>ldiv.o</t>
   </si>
   <si>
     <t>__dczerorl2.o</t>
@@ -248,16 +257,16 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$40</c:f>
+              <c:f>ram_percent!$A$3:$A$43</c:f>
               <c:strCache>
-                <c:ptCount val="38"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-bc9b39.o</c:v>
+                  <c:v>lto-llvm-44c51f.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>startup_at32f415.o</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="40">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -265,17 +274,17 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$40</c:f>
+              <c:f>ram_percent!$B$3:$B$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="38"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
-                  <c:v>83.04916381835938</c:v>
+                  <c:v>83.73570251464844</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>16.95083618164063</c:v>
-                </c:pt>
-                <c:pt idx="37">
+                  <c:v>16.26429557800293</c:v>
+                </c:pt>
+                <c:pt idx="40">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -343,11 +352,11 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$40</c:f>
+              <c:f>flash_percent!$A$3:$A$43</c:f>
               <c:strCache>
-                <c:ptCount val="38"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-bc9b39.o</c:v>
+                  <c:v>lto-llvm-44c51f.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>mf_w.l</c:v>
@@ -365,99 +374,108 @@
                   <c:v>dmul.o</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>ddiv.o</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>depilogue.o</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>fadd.o</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
+                  <c:v>fdiv.o</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>fepilogue.o</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>fmul.o</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="12">
                   <c:v>uldiv.o</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="13">
+                  <c:v>ldiv.o</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>__dczerorl2.o</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="15">
                   <c:v>d2f.o</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="16">
                   <c:v>ffixi.o</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="17">
                   <c:v>dfixui.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="18">
                   <c:v>init.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="19">
                   <c:v>ffixui.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="20">
                   <c:v>cpp_init.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="21">
                   <c:v>f2d.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="22">
                   <c:v>memseta.o</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="23">
                   <c:v>llsshr.o</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="24">
                   <c:v>llushr.o</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="25">
                   <c:v>llshl.o</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="26">
                   <c:v>handlers.o</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="27">
                   <c:v>fcmplt.o</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="28">
                   <c:v>fcmple.o</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="29">
                   <c:v>fcmpgt.o</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="30">
                   <c:v>fcmpge.o</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="31">
                   <c:v>fcmpeq.o</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="32">
                   <c:v>systick_wrapper_gnu.o</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="33">
                   <c:v>dfltui.o</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="34">
                   <c:v>fflti.o</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="35">
                   <c:v>ffltui.o</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="36">
                   <c:v>entry9a.o</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="37">
                   <c:v>entry2.o</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="38">
                   <c:v>entry8a.o</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="39">
                   <c:v>entry5.o</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="40">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -465,122 +483,131 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$40</c:f>
+              <c:f>flash_percent!$B$3:$B$43</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="38"/>
+                <c:ptCount val="41"/>
                 <c:pt idx="0">
-                  <c:v>87.76313781738281</c:v>
+                  <c:v>90.2279052734375</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.270326614379883</c:v>
+                  <c:v>3.475979566574097</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.257586479187012</c:v>
+                  <c:v>1.016560077667236</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.104489088058472</c:v>
+                  <c:v>0.7360040545463562</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.9131171703338623</c:v>
+                  <c:v>0.6084786057472229</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.6233254671096802</c:v>
+                  <c:v>0.4153686463832855</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.5085023641586304</c:v>
+                  <c:v>0.4044378995895386</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.4811635315418243</c:v>
+                  <c:v>0.3388533592224121</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.3007272183895111</c:v>
+                  <c:v>0.3206354379653931</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.2733883857727051</c:v>
+                  <c:v>0.2259022444486618</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.2679206132888794</c:v>
+                  <c:v>0.2003971487283707</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.2351140081882477</c:v>
+                  <c:v>0.1821792274713516</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.1530974954366684</c:v>
+                  <c:v>0.1785356402397156</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.1366941928863525</c:v>
+                  <c:v>0.1785356402397156</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.1366941928863525</c:v>
+                  <c:v>0.1566741317510605</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.1312264204025269</c:v>
+                  <c:v>0.1020203679800034</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.1093553528189659</c:v>
+                  <c:v>0.09108961373567581</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.1093553528189659</c:v>
+                  <c:v>0.09108961373567581</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.1038875803351402</c:v>
+                  <c:v>0.08744602650403976</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.09841981530189514</c:v>
+                  <c:v>0.07287169247865677</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.09841981530189514</c:v>
+                  <c:v>0.07287169247865677</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.08748427778482437</c:v>
+                  <c:v>0.06922810524702072</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.08201651275157929</c:v>
+                  <c:v>0.06558452546596527</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.08201651275157929</c:v>
+                  <c:v>0.06558452546596527</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.0765487477183342</c:v>
+                  <c:v>0.05829735472798348</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.0765487477183342</c:v>
+                  <c:v>0.05465376749634743</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.0765487477183342</c:v>
+                  <c:v>0.05465376749634743</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.0765487477183342</c:v>
+                  <c:v>0.05101018399000168</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.0765487477183342</c:v>
+                  <c:v>0.05101018399000168</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.0765487477183342</c:v>
+                  <c:v>0.05101018399000168</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.07108097523450851</c:v>
+                  <c:v>0.05101018399000168</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.04920990765094757</c:v>
+                  <c:v>0.05101018399000168</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.02733883820474148</c:v>
+                  <c:v>0.05101018399000168</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.02187106944620609</c:v>
+                  <c:v>0.04736660048365593</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.02187106944620609</c:v>
+                  <c:v>0.03279226273298264</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.01093553472310305</c:v>
+                  <c:v>0.01821792311966419</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.01093553472310305</c:v>
+                  <c:v>0.01457433868199587</c:v>
                 </c:pt>
                 <c:pt idx="37">
+                  <c:v>0.01457433868199587</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.007287169340997934</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.007287169340997934</c:v>
+                </c:pt>
+                <c:pt idx="40">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -685,8 +712,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H40" totalsRowCount="1">
-  <autoFilter ref="A2:H39"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H43" totalsRowCount="1">
+  <autoFilter ref="A2:H42"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -702,8 +729,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H40" totalsRowCount="1">
-  <autoFilter ref="A2:H39"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H43" totalsRowCount="1">
+  <autoFilter ref="A2:H42"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -1003,7 +1030,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1016,28 +1043,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1045,25 +1072,25 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>83.04916381835938</v>
+        <v>83.73570251464844</v>
       </c>
       <c r="C3" s="1">
-        <v>5017</v>
+        <v>5272</v>
       </c>
       <c r="D3" s="1">
-        <v>32102</v>
+        <v>49527</v>
       </c>
       <c r="E3" s="1">
-        <v>31570</v>
+        <v>48964</v>
       </c>
       <c r="F3" s="1">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="G3" s="1">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="H3" s="1">
-        <v>4703</v>
+        <v>4940</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1071,7 +1098,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>16.95083618164063</v>
+        <v>16.26429557800293</v>
       </c>
       <c r="C4" s="1">
         <v>1024</v>
@@ -1092,35 +1119,35 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
-      <c r="A40" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40">
+    <row r="43" spans="1:8">
+      <c r="A43" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C40">
+      <c r="C43">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D40">
+      <c r="D43">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E40">
+      <c r="E43">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F40">
+      <c r="F43">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G40">
+      <c r="G43">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H40">
+      <c r="H43">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -1136,7 +1163,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1149,28 +1176,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" t="s">
         <v>47</v>
       </c>
-      <c r="C2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F2" t="s">
-        <v>44</v>
-      </c>
       <c r="G2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1178,25 +1205,25 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>87.76313781738281</v>
+        <v>90.2279052734375</v>
       </c>
       <c r="C3" s="1">
-        <v>32102</v>
+        <v>49527</v>
       </c>
       <c r="D3" s="1">
-        <v>5017</v>
+        <v>5272</v>
       </c>
       <c r="E3" s="1">
-        <v>31570</v>
+        <v>48964</v>
       </c>
       <c r="F3" s="1">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="G3" s="1">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="H3" s="1">
-        <v>4703</v>
+        <v>4940</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1204,16 +1231,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>4.270326614379883</v>
+        <v>3.475979566574097</v>
       </c>
       <c r="C4" s="1">
-        <v>1562</v>
+        <v>1908</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
       </c>
       <c r="E4" s="1">
-        <v>1562</v>
+        <v>1908</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -1230,16 +1257,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>1.257586479187012</v>
+        <v>1.016560077667236</v>
       </c>
       <c r="C5" s="1">
-        <v>460</v>
+        <v>558</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
       </c>
       <c r="E5" s="1">
-        <v>460</v>
+        <v>558</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -1256,7 +1283,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2">
-        <v>1.104489088058472</v>
+        <v>0.7360040545463562</v>
       </c>
       <c r="C6" s="1">
         <v>404</v>
@@ -1282,7 +1309,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>0.9131171703338623</v>
+        <v>0.6084786057472229</v>
       </c>
       <c r="C7" s="1">
         <v>334</v>
@@ -1308,7 +1335,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.6233254671096802</v>
+        <v>0.4153686463832855</v>
       </c>
       <c r="C8" s="1">
         <v>228</v>
@@ -1334,16 +1361,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.5085023641586304</v>
+        <v>0.4044378995895386</v>
       </c>
       <c r="C9" s="1">
-        <v>186</v>
+        <v>222</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
       </c>
       <c r="E9" s="1">
-        <v>186</v>
+        <v>222</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -1360,16 +1387,16 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.4811635315418243</v>
+        <v>0.3388533592224121</v>
       </c>
       <c r="C10" s="1">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
       </c>
       <c r="E10" s="1">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
@@ -1386,16 +1413,16 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.3007272183895111</v>
+        <v>0.3206354379653931</v>
       </c>
       <c r="C11" s="1">
-        <v>110</v>
+        <v>176</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
       </c>
       <c r="E11" s="1">
-        <v>110</v>
+        <v>176</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
@@ -1412,16 +1439,16 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.2733883857727051</v>
+        <v>0.2259022444486618</v>
       </c>
       <c r="C12" s="1">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
       </c>
       <c r="E12" s="1">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -1438,16 +1465,16 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.2679206132888794</v>
+        <v>0.2003971487283707</v>
       </c>
       <c r="C13" s="1">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
       </c>
       <c r="E13" s="1">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
@@ -1464,16 +1491,16 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.2351140081882477</v>
+        <v>0.1821792274713516</v>
       </c>
       <c r="C14" s="1">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
       </c>
       <c r="E14" s="1">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -1490,16 +1517,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.1530974954366684</v>
+        <v>0.1785356402397156</v>
       </c>
       <c r="C15" s="1">
-        <v>56</v>
+        <v>98</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
       </c>
       <c r="E15" s="1">
-        <v>56</v>
+        <v>98</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
@@ -1516,16 +1543,16 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.1366941928863525</v>
+        <v>0.1785356402397156</v>
       </c>
       <c r="C16" s="1">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
       </c>
       <c r="E16" s="1">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
@@ -1542,16 +1569,16 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.1366941928863525</v>
+        <v>0.1566741317510605</v>
       </c>
       <c r="C17" s="1">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
       </c>
       <c r="E17" s="1">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -1568,16 +1595,16 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.1312264204025269</v>
+        <v>0.1020203679800034</v>
       </c>
       <c r="C18" s="1">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
       </c>
       <c r="E18" s="1">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -1594,16 +1621,16 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.1093553528189659</v>
+        <v>0.09108961373567581</v>
       </c>
       <c r="C19" s="1">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
       </c>
       <c r="E19" s="1">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -1620,16 +1647,16 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.1093553528189659</v>
+        <v>0.09108961373567581</v>
       </c>
       <c r="C20" s="1">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
       </c>
       <c r="E20" s="1">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -1646,16 +1673,16 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.1038875803351402</v>
+        <v>0.08744602650403976</v>
       </c>
       <c r="C21" s="1">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
       </c>
       <c r="E21" s="1">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -1672,16 +1699,16 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.09841981530189514</v>
+        <v>0.07287169247865677</v>
       </c>
       <c r="C22" s="1">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
       </c>
       <c r="E22" s="1">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -1698,16 +1725,16 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.09841981530189514</v>
+        <v>0.07287169247865677</v>
       </c>
       <c r="C23" s="1">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
       </c>
       <c r="E23" s="1">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
@@ -1724,16 +1751,16 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.08748427778482437</v>
+        <v>0.06922810524702072</v>
       </c>
       <c r="C24" s="1">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
       </c>
       <c r="E24" s="1">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -1750,16 +1777,16 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.08201651275157929</v>
+        <v>0.06558452546596527</v>
       </c>
       <c r="C25" s="1">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
       </c>
       <c r="E25" s="1">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -1776,16 +1803,16 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.08201651275157929</v>
+        <v>0.06558452546596527</v>
       </c>
       <c r="C26" s="1">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D26" s="1">
         <v>0</v>
       </c>
       <c r="E26" s="1">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -1802,16 +1829,16 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.0765487477183342</v>
+        <v>0.05829735472798348</v>
       </c>
       <c r="C27" s="1">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
       </c>
       <c r="E27" s="1">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
@@ -1828,16 +1855,16 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.0765487477183342</v>
+        <v>0.05465376749634743</v>
       </c>
       <c r="C28" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
       </c>
       <c r="E28" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -1854,16 +1881,16 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.0765487477183342</v>
+        <v>0.05465376749634743</v>
       </c>
       <c r="C29" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
       </c>
       <c r="E29" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
@@ -1880,7 +1907,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.0765487477183342</v>
+        <v>0.05101018399000168</v>
       </c>
       <c r="C30" s="1">
         <v>28</v>
@@ -1906,7 +1933,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.0765487477183342</v>
+        <v>0.05101018399000168</v>
       </c>
       <c r="C31" s="1">
         <v>28</v>
@@ -1932,7 +1959,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.0765487477183342</v>
+        <v>0.05101018399000168</v>
       </c>
       <c r="C32" s="1">
         <v>28</v>
@@ -1958,16 +1985,16 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.07108097523450851</v>
+        <v>0.05101018399000168</v>
       </c>
       <c r="C33" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
       </c>
       <c r="E33" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
@@ -1984,16 +2011,16 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.04920990765094757</v>
+        <v>0.05101018399000168</v>
       </c>
       <c r="C34" s="1">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D34" s="1">
         <v>0</v>
       </c>
       <c r="E34" s="1">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F34" s="1">
         <v>0</v>
@@ -2010,16 +2037,16 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.02733883820474148</v>
+        <v>0.05101018399000168</v>
       </c>
       <c r="C35" s="1">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="D35" s="1">
         <v>0</v>
       </c>
       <c r="E35" s="1">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
@@ -2036,16 +2063,16 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.02187106944620609</v>
+        <v>0.04736660048365593</v>
       </c>
       <c r="C36" s="1">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D36" s="1">
         <v>0</v>
       </c>
       <c r="E36" s="1">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
@@ -2062,16 +2089,16 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.02187106944620609</v>
+        <v>0.03279226273298264</v>
       </c>
       <c r="C37" s="1">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D37" s="1">
         <v>0</v>
       </c>
       <c r="E37" s="1">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
@@ -2088,16 +2115,16 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.01093553472310305</v>
+        <v>0.01821792311966419</v>
       </c>
       <c r="C38" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D38" s="1">
         <v>0</v>
       </c>
       <c r="E38" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
@@ -2114,56 +2141,134 @@
         <v>37</v>
       </c>
       <c r="B39" s="2">
-        <v>0.01093553472310305</v>
+        <v>0.01457433868199587</v>
       </c>
       <c r="C39" s="1">
+        <v>8</v>
+      </c>
+      <c r="D39" s="1">
+        <v>0</v>
+      </c>
+      <c r="E39" s="1">
+        <v>8</v>
+      </c>
+      <c r="F39" s="1">
+        <v>0</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="2">
+        <v>0.01457433868199587</v>
+      </c>
+      <c r="C40" s="1">
+        <v>8</v>
+      </c>
+      <c r="D40" s="1">
+        <v>0</v>
+      </c>
+      <c r="E40" s="1">
+        <v>8</v>
+      </c>
+      <c r="F40" s="1">
+        <v>0</v>
+      </c>
+      <c r="G40" s="1">
+        <v>0</v>
+      </c>
+      <c r="H40" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="2">
+        <v>0.007287169340997934</v>
+      </c>
+      <c r="C41" s="1">
         <v>4</v>
       </c>
-      <c r="D39" s="1">
-        <v>0</v>
-      </c>
-      <c r="E39" s="1">
+      <c r="D41" s="1">
+        <v>0</v>
+      </c>
+      <c r="E41" s="1">
         <v>4</v>
       </c>
-      <c r="F39" s="1">
-        <v>0</v>
-      </c>
-      <c r="G39" s="1">
-        <v>0</v>
-      </c>
-      <c r="H39" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40">
+      <c r="F41" s="1">
+        <v>0</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0</v>
+      </c>
+      <c r="H41" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="2">
+        <v>0.007287169340997934</v>
+      </c>
+      <c r="C42" s="1">
+        <v>4</v>
+      </c>
+      <c r="D42" s="1">
+        <v>0</v>
+      </c>
+      <c r="E42" s="1">
+        <v>4</v>
+      </c>
+      <c r="F42" s="1">
+        <v>0</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C40">
+      <c r="C43">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D40">
+      <c r="D43">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E40">
+      <c r="E43">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F40">
+      <c r="F43">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G40">
+      <c r="G43">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H40">
+      <c r="H43">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
